--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,7 +612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -678,7 +693,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -759,7 +774,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -840,7 +855,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -921,7 +936,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1002,7 +1017,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1083,7 +1098,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1164,7 +1179,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1245,7 +1260,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1326,7 +1341,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1407,7 +1422,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1488,7 +1503,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1569,7 +1584,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1650,7 +1665,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1731,7 +1746,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1812,7 +1827,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1893,7 +1908,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1974,7 +1989,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2055,7 +2070,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2136,7 +2151,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2217,7 +2232,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2298,7 +2313,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2379,7 +2394,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2460,7 +2475,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2541,7 +2556,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2622,7 +2637,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2703,7 +2718,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2784,7 +2799,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2865,7 +2880,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2946,7 +2961,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -3027,7 +3042,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3108,7 +3123,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3189,7 +3204,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3270,7 +3285,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3351,7 +3366,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3432,7 +3447,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3513,7 +3528,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3594,7 +3609,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3675,7 +3690,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3756,7 +3771,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3837,7 +3852,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3918,7 +3933,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3999,7 +4014,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -4080,7 +4095,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4161,7 +4176,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4242,7 +4257,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4323,7 +4338,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4404,7 +4419,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4485,7 +4500,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4566,7 +4581,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4647,7 +4662,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4728,7 +4743,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4809,7 +4824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4890,7 +4905,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4971,7 +4986,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -5052,7 +5067,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -5133,7 +5148,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5214,7 +5229,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5295,7 +5310,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5376,7 +5391,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5457,7 +5472,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5538,7 +5553,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5619,7 +5634,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5700,7 +5715,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5781,7 +5796,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5862,7 +5877,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5943,7 +5958,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -6024,7 +6039,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -6105,7 +6120,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -6186,7 +6201,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6267,7 +6282,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6348,7 +6363,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6429,7 +6444,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6510,7 +6525,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6591,7 +6606,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6672,7 +6687,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6753,7 +6768,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6834,7 +6849,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6915,7 +6930,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6996,7 +7011,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -7077,7 +7092,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -7158,7 +7173,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -7239,7 +7254,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7320,7 +7335,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7401,7 +7416,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7482,7 +7497,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7563,7 +7578,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7644,7 +7659,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7725,7 +7740,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7806,7 +7821,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7887,7 +7902,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7968,7 +7983,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -8049,7 +8064,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -8130,7 +8145,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -8211,7 +8226,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8292,7 +8307,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8373,7 +8388,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8454,7 +8469,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8535,7 +8550,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8616,7 +8631,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8697,7 +8712,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8778,7 +8793,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8859,7 +8874,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8940,7 +8955,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -9021,7 +9036,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -9102,7 +9117,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -9183,7 +9198,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -9264,7 +9279,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9345,7 +9360,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9426,7 +9441,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9507,7 +9522,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9588,7 +9603,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9669,7 +9684,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9750,7 +9765,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9831,7 +9846,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9912,7 +9927,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9993,7 +10008,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -10074,7 +10089,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -10155,7 +10170,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -10236,7 +10251,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -10317,7 +10332,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10398,7 +10413,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10479,7 +10494,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10560,7 +10575,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10641,7 +10656,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10722,7 +10737,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10803,7 +10818,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10884,7 +10899,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10965,7 +10980,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -11046,7 +11061,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -11127,7 +11142,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -11208,7 +11223,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -11289,7 +11304,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -11370,7 +11385,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11451,7 +11466,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11532,7 +11547,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11613,7 +11628,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11694,7 +11709,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11775,7 +11790,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11856,7 +11871,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11937,7 +11952,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -12018,7 +12033,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -12099,7 +12114,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -12180,7 +12195,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -12261,7 +12276,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -12342,7 +12357,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -12423,7 +12438,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12504,7 +12519,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12585,7 +12600,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12666,7 +12681,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12747,7 +12762,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12828,7 +12843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12909,7 +12924,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12990,7 +13005,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -13071,7 +13086,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -13152,7 +13167,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -13233,7 +13248,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -13314,7 +13329,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -13395,7 +13410,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -13476,7 +13491,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13557,7 +13572,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13638,7 +13653,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13719,7 +13734,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13800,7 +13815,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13881,7 +13896,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13962,7 +13977,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -14043,7 +14058,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -14124,7 +14139,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -14205,7 +14220,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -14286,7 +14301,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -14367,7 +14382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -14448,7 +14463,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -14529,7 +14544,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14610,7 +14625,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14691,7 +14706,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14772,7 +14787,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14853,7 +14868,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14934,7 +14949,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -15015,7 +15030,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -15096,7 +15111,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -15177,7 +15192,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -15258,7 +15273,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -15339,7 +15354,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -15420,7 +15435,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -15501,7 +15516,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15582,7 +15597,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15663,7 +15678,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15744,7 +15759,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15825,7 +15840,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15906,7 +15921,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15987,7 +16002,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -16068,7 +16083,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -16149,7 +16164,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -16230,7 +16245,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -16311,7 +16326,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -16392,7 +16407,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -16473,7 +16488,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -16554,7 +16569,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16635,7 +16650,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16716,7 +16731,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16797,7 +16812,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16878,7 +16893,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16959,7 +16974,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -17040,7 +17055,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -17121,7 +17136,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -17202,7 +17217,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -17283,7 +17298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -17364,7 +17379,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -17445,7 +17460,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -17526,7 +17541,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -17607,7 +17622,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17688,7 +17703,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17769,7 +17784,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17850,7 +17865,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17931,7 +17946,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -18012,7 +18027,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -18093,7 +18108,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -18174,7 +18189,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -18255,7 +18270,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -18336,7 +18351,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -18417,7 +18432,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="4" t="n">
+      <c r="G227" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -18498,7 +18513,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="4" t="n">
+      <c r="G228" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -18579,7 +18594,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="4" t="n">
+      <c r="G229" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -18660,7 +18675,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="4" t="n">
+      <c r="G230" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18741,7 +18756,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="4" t="n">
+      <c r="G231" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18822,7 +18837,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="4" t="n">
+      <c r="G232" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18903,7 +18918,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="4" t="n">
+      <c r="G233" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18984,7 +18999,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="4" t="n">
+      <c r="G234" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -19065,7 +19080,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="4" t="n">
+      <c r="G235" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -19146,7 +19161,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="4" t="n">
+      <c r="G236" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -19227,7 +19242,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="4" t="n">
+      <c r="G237" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -19308,7 +19323,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="4" t="n">
+      <c r="G238" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -19389,7 +19404,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="4" t="n">
+      <c r="G239" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -19470,7 +19485,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="4" t="n">
+      <c r="G240" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -19551,7 +19566,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="4" t="n">
+      <c r="G241" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -19632,7 +19647,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n">
+      <c r="G242" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -19713,7 +19728,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
+      <c r="G243" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19794,7 +19809,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
+      <c r="G244" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19875,7 +19890,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="4" t="n">
+      <c r="G245" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19956,7 +19971,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="4" t="n">
+      <c r="G246" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -20037,7 +20052,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n">
+      <c r="G247" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -20118,7 +20133,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n">
+      <c r="G248" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -20199,7 +20214,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="4" t="n">
+      <c r="G249" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -20280,7 +20295,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="4" t="n">
+      <c r="G250" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -20361,7 +20376,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="4" t="n">
+      <c r="G251" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -20442,7 +20457,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="4" t="n">
+      <c r="G252" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -20523,7 +20538,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="4" t="n">
+      <c r="G253" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -20604,7 +20619,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="4" t="n">
+      <c r="G254" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -20685,7 +20700,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="4" t="n">
+      <c r="G255" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -20766,7 +20781,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="4" t="n">
+      <c r="G256" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20847,7 +20862,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="4" t="n">
+      <c r="G257" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20928,7 +20943,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="4" t="n">
+      <c r="G258" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -21009,7 +21024,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="4" t="n">
+      <c r="G259" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -21090,7 +21105,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="4" t="n">
+      <c r="G260" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -21171,7 +21186,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="4" t="n">
+      <c r="G261" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -21252,7 +21267,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
+      <c r="G262" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -21333,7 +21348,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
+      <c r="G263" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -21414,7 +21429,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
+      <c r="G264" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -21495,7 +21510,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
+      <c r="G265" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -21576,7 +21591,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
+      <c r="G266" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -21657,7 +21672,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
+      <c r="G267" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -21738,7 +21753,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
+      <c r="G268" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21819,7 +21834,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
+      <c r="G269" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21900,7 +21915,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
+      <c r="G270" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21981,7 +21996,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="4" t="n">
+      <c r="G271" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
@@ -22062,7 +22077,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="4" t="n">
+      <c r="G272" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -22143,7 +22158,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="4" t="n">
+      <c r="G273" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -22224,7 +22239,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="4" t="n">
+      <c r="G274" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -22305,7 +22320,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G275" s="4" t="n">
+      <c r="G275" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -22386,7 +22401,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G276" s="4" t="n">
+      <c r="G276" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
@@ -22467,7 +22482,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G277" s="4" t="n">
+      <c r="G277" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
@@ -22548,7 +22563,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G278" s="4" t="n">
+      <c r="G278" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
@@ -22629,7 +22644,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G279" s="4" t="n">
+      <c r="G279" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
@@ -22710,7 +22725,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G280" s="4" t="n">
+      <c r="G280" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
@@ -22791,7 +22806,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G281" s="4" t="n">
+      <c r="G281" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
@@ -22872,7 +22887,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G282" s="4" t="n">
+      <c r="G282" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
@@ -22953,7 +22968,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G283" s="4" t="n">
+      <c r="G283" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
@@ -23034,7 +23049,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G284" s="4" t="n">
+      <c r="G284" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
@@ -23115,7 +23130,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G285" s="4" t="n">
+      <c r="G285" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
@@ -23196,7 +23211,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G286" s="4" t="n">
+      <c r="G286" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
@@ -23277,7 +23292,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G287" s="4" t="n">
+      <c r="G287" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
@@ -23358,7 +23373,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G288" s="4" t="n">
+      <c r="G288" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
@@ -23439,7 +23454,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G289" s="4" t="n">
+      <c r="G289" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
@@ -23520,7 +23535,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G290" s="4" t="n">
+      <c r="G290" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
@@ -23601,7 +23616,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G291" s="4" t="n">
+      <c r="G291" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
@@ -23682,7 +23697,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G292" s="4" t="n">
+      <c r="G292" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
@@ -23763,7 +23778,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G293" s="4" t="n">
+      <c r="G293" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
@@ -23844,7 +23859,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G294" s="4" t="n">
+      <c r="G294" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
@@ -23925,7 +23940,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G295" s="4" t="n">
+      <c r="G295" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
@@ -24006,7 +24021,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G296" s="4" t="n">
+      <c r="G296" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
@@ -24087,7 +24102,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G297" s="4" t="n">
+      <c r="G297" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
@@ -24168,7 +24183,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G298" s="4" t="n">
+      <c r="G298" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
@@ -24249,7 +24264,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G299" s="4" t="n">
+      <c r="G299" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -24330,7 +24345,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G300" s="4" t="n">
+      <c r="G300" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -24411,7 +24426,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G301" s="4" t="n">
+      <c r="G301" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -24492,7 +24507,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G302" s="4" t="n">
+      <c r="G302" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -24573,7 +24588,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G303" s="4" t="n">
+      <c r="G303" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
@@ -24654,7 +24669,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G304" s="4" t="n">
+      <c r="G304" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
@@ -24735,7 +24750,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G305" s="4" t="n">
+      <c r="G305" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
@@ -24816,7 +24831,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G306" s="4" t="n">
+      <c r="G306" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -24897,7 +24912,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G307" s="4" t="n">
+      <c r="G307" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -24978,7 +24993,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G308" s="4" t="n">
+      <c r="G308" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
@@ -25059,7 +25074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G309" s="4" t="n">
+      <c r="G309" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
@@ -25140,7 +25155,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G310" s="4" t="n">
+      <c r="G310" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
@@ -25221,7 +25236,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G311" s="4" t="n">
+      <c r="G311" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
@@ -25302,7 +25317,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G312" s="4" t="n">
+      <c r="G312" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
@@ -25383,7 +25398,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G313" s="4" t="n">
+      <c r="G313" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
@@ -25464,7 +25479,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G314" s="4" t="n">
+      <c r="G314" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
@@ -25545,7 +25560,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G315" s="4" t="n">
+      <c r="G315" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
@@ -25626,7 +25641,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G316" s="4" t="n">
+      <c r="G316" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
@@ -25707,7 +25722,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G317" s="4" t="n">
+      <c r="G317" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
@@ -25788,7 +25803,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G318" s="4" t="n">
+      <c r="G318" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
@@ -25869,7 +25884,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G319" s="4" t="n">
+      <c r="G319" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
@@ -25950,7 +25965,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G320" s="4" t="n">
+      <c r="G320" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
@@ -26031,7 +26046,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G321" s="4" t="n">
+      <c r="G321" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
@@ -26112,7 +26127,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G322" s="4" t="n">
+      <c r="G322" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
@@ -26193,7 +26208,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G323" s="4" t="n">
+      <c r="G323" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
@@ -26274,7 +26289,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G324" s="4" t="n">
+      <c r="G324" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
@@ -26355,7 +26370,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G325" s="4" t="n">
+      <c r="G325" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
@@ -26436,7 +26451,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G326" s="4" t="n">
+      <c r="G326" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
@@ -26517,7 +26532,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G327" s="4" t="n">
+      <c r="G327" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
@@ -26598,7 +26613,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G328" s="4" t="n">
+      <c r="G328" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
@@ -26679,7 +26694,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G329" s="4" t="n">
+      <c r="G329" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -26760,7 +26775,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G330" s="4" t="n">
+      <c r="G330" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
@@ -26841,7 +26856,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G331" s="4" t="n">
+      <c r="G331" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
@@ -26922,7 +26937,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G332" s="4" t="n">
+      <c r="G332" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
@@ -27003,7 +27018,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G333" s="4" t="n">
+      <c r="G333" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
@@ -27084,7 +27099,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G334" s="4" t="n">
+      <c r="G334" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
@@ -27165,7 +27180,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G335" s="4" t="n">
+      <c r="G335" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
@@ -27246,7 +27261,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G336" s="4" t="n">
+      <c r="G336" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
@@ -27327,7 +27342,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G337" s="4" t="n">
+      <c r="G337" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
@@ -27408,7 +27423,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G338" s="4" t="n">
+      <c r="G338" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H338" s="4" t="inlineStr">
@@ -27489,7 +27504,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G339" s="4" t="n">
+      <c r="G339" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H339" s="4" t="inlineStr">
@@ -27570,7 +27585,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G340" s="4" t="n">
+      <c r="G340" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H340" s="4" t="inlineStr">
@@ -27651,7 +27666,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G341" s="4" t="n">
+      <c r="G341" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H341" s="4" t="inlineStr">
@@ -27732,7 +27747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G342" s="4" t="n">
+      <c r="G342" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H342" s="4" t="inlineStr">
@@ -27809,7 +27824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G343" s="4" t="n">
+      <c r="G343" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H343" s="4" t="inlineStr">
@@ -27842,7 +27857,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N343" s="4" t="n">
+      <c r="N343" s="8" t="n">
         <v>2.01373056168983</v>
       </c>
       <c r="O343" s="4" t="inlineStr">
@@ -27888,7 +27903,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G344" s="4" t="n">
+      <c r="G344" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H344" s="4" t="inlineStr">
@@ -27921,7 +27936,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N344" s="4" t="n">
+      <c r="N344" s="8" t="n">
         <v>0.6650541384622241</v>
       </c>
       <c r="O344" s="4" t="inlineStr">
@@ -27967,7 +27982,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G345" s="4" t="n">
+      <c r="G345" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H345" s="4" t="inlineStr">
@@ -28000,7 +28015,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N345" s="4" t="n">
+      <c r="N345" s="8" t="n">
         <v>4.91982977988773</v>
       </c>
       <c r="O345" s="4" t="inlineStr">
@@ -28046,7 +28061,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G346" s="4" t="n">
+      <c r="G346" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H346" s="4" t="inlineStr">
@@ -28079,7 +28094,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N346" s="4" t="n">
+      <c r="N346" s="8" t="n">
         <v>-0.366502858122402</v>
       </c>
       <c r="O346" s="4" t="inlineStr">
@@ -28125,7 +28140,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G347" s="4" t="n">
+      <c r="G347" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H347" s="4" t="inlineStr">
@@ -28158,7 +28173,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N347" s="4" t="n">
+      <c r="N347" s="8" t="n">
         <v>2.16720883620505</v>
       </c>
       <c r="O347" s="4" t="inlineStr">
@@ -28204,7 +28219,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G348" s="4" t="n">
+      <c r="G348" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H348" s="4" t="inlineStr">
@@ -28237,7 +28252,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N348" s="4" t="n">
+      <c r="N348" s="8" t="n">
         <v>2.64492682981677</v>
       </c>
       <c r="O348" s="4" t="inlineStr">
@@ -28283,7 +28298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G349" s="4" t="n">
+      <c r="G349" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H349" s="4" t="inlineStr">
@@ -28316,7 +28331,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N349" s="4" t="n">
+      <c r="N349" s="8" t="n">
         <v>2.43422682068099</v>
       </c>
       <c r="O349" s="4" t="inlineStr">
@@ -28362,7 +28377,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G350" s="4" t="n">
+      <c r="G350" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H350" s="4" t="inlineStr">
@@ -28395,7 +28410,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N350" s="4" t="n">
+      <c r="N350" s="8" t="n">
         <v>1.06509902850236</v>
       </c>
       <c r="O350" s="4" t="inlineStr">
@@ -28441,7 +28456,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G351" s="4" t="n">
+      <c r="G351" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H351" s="4" t="inlineStr">
@@ -28474,7 +28489,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N351" s="4" t="n">
+      <c r="N351" s="8" t="n">
         <v>1.77946177900719</v>
       </c>
       <c r="O351" s="4" t="inlineStr">
@@ -28520,7 +28535,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G352" s="4" t="n">
+      <c r="G352" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H352" s="4" t="inlineStr">
@@ -28553,7 +28568,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N352" s="4" t="n">
+      <c r="N352" s="8" t="n">
         <v>4.35826317842816</v>
       </c>
       <c r="O352" s="4" t="inlineStr">
@@ -28599,7 +28614,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G353" s="4" t="n">
+      <c r="G353" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H353" s="4" t="inlineStr">
@@ -28632,7 +28647,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N353" s="4" t="n">
+      <c r="N353" s="8" t="n">
         <v>8.232657591742679</v>
       </c>
       <c r="O353" s="4" t="inlineStr">
@@ -28678,7 +28693,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G354" s="4" t="n">
+      <c r="G354" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H354" s="4" t="inlineStr">
@@ -28711,7 +28726,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N354" s="4" t="n">
+      <c r="N354" s="8" t="n">
         <v>6.26877681900034</v>
       </c>
       <c r="O354" s="4" t="inlineStr">
@@ -28757,7 +28772,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G355" s="4" t="n">
+      <c r="G355" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H355" s="4" t="inlineStr">
@@ -28790,7 +28805,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N355" s="4" t="n">
+      <c r="N355" s="8" t="n">
         <v>11.2003944899522</v>
       </c>
       <c r="O355" s="4" t="inlineStr">
@@ -28836,7 +28851,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G356" s="4" t="n">
+      <c r="G356" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H356" s="4" t="inlineStr">
@@ -28869,7 +28884,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N356" s="4" t="n">
+      <c r="N356" s="8" t="n">
         <v>50.107968794629</v>
       </c>
       <c r="O356" s="4" t="inlineStr">
@@ -28915,7 +28930,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G357" s="4" t="n">
+      <c r="G357" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H357" s="4" t="inlineStr">
@@ -28948,7 +28963,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N357" s="4" t="n">
+      <c r="N357" s="8" t="n">
         <v>2.26299814945894</v>
       </c>
       <c r="O357" s="4" t="inlineStr">
@@ -28994,7 +29009,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G358" s="4" t="n">
+      <c r="G358" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H358" s="4" t="inlineStr">
@@ -29027,7 +29042,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N358" s="4" t="n">
+      <c r="N358" s="8" t="n">
         <v>6.19354432405103</v>
       </c>
       <c r="O358" s="4" t="inlineStr">
@@ -29073,7 +29088,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G359" s="4" t="n">
+      <c r="G359" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H359" s="4" t="inlineStr">
@@ -29106,7 +29121,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N359" s="4" t="n">
+      <c r="N359" s="8" t="n">
         <v>8.44842727068664</v>
       </c>
       <c r="O359" s="4" t="inlineStr">
@@ -29152,7 +29167,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G360" s="4" t="n">
+      <c r="G360" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H360" s="4" t="inlineStr">
@@ -29185,7 +29200,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N360" s="4" t="n">
+      <c r="N360" s="8" t="n">
         <v>6.08667532833461</v>
       </c>
       <c r="O360" s="4" t="inlineStr">
@@ -29231,7 +29246,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G361" s="4" t="n">
+      <c r="G361" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H361" s="4" t="inlineStr">
@@ -29264,7 +29279,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N361" s="4" t="n">
+      <c r="N361" s="8" t="n">
         <v>21.9455792548796</v>
       </c>
       <c r="O361" s="4" t="inlineStr">
@@ -29310,7 +29325,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G362" s="4" t="n">
+      <c r="G362" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H362" s="4" t="inlineStr">
@@ -29343,7 +29358,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N362" s="4" t="n">
+      <c r="N362" s="8" t="n">
         <v>28.0272395381622</v>
       </c>
       <c r="O362" s="4" t="inlineStr">
@@ -29389,7 +29404,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G363" s="4" t="n">
+      <c r="G363" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H363" s="4" t="inlineStr">
@@ -29422,7 +29437,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N363" s="4" t="n">
+      <c r="N363" s="8" t="n">
         <v>13.6316657569901</v>
       </c>
       <c r="O363" s="4" t="inlineStr">
@@ -29468,7 +29483,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G364" s="4" t="n">
+      <c r="G364" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H364" s="4" t="inlineStr">
@@ -29501,7 +29516,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N364" s="4" t="n">
+      <c r="N364" s="8" t="n">
         <v>-0.42040040122437</v>
       </c>
       <c r="O364" s="4" t="inlineStr">
@@ -29547,7 +29562,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G365" s="4" t="n">
+      <c r="G365" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H365" s="4" t="inlineStr">
@@ -29580,7 +29595,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N365" s="4" t="n">
+      <c r="N365" s="8" t="n">
         <v>10.3947543511296</v>
       </c>
       <c r="O365" s="4" t="inlineStr">
@@ -29626,7 +29641,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G366" s="4" t="n">
+      <c r="G366" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H366" s="4" t="inlineStr">
@@ -29659,7 +29674,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N366" s="4" t="n">
+      <c r="N366" s="8" t="n">
         <v>37.4952567752211</v>
       </c>
       <c r="O366" s="4" t="inlineStr">
@@ -29705,7 +29720,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G367" s="4" t="n">
+      <c r="G367" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H367" s="4" t="inlineStr">
@@ -29738,7 +29753,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N367" s="4" t="n">
+      <c r="N367" s="8" t="n">
         <v>9.91291286624789</v>
       </c>
       <c r="O367" s="4" t="inlineStr">
@@ -29784,7 +29799,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G368" s="4" t="n">
+      <c r="G368" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H368" s="4" t="inlineStr">
@@ -29817,7 +29832,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N368" s="4" t="n">
+      <c r="N368" s="8" t="n">
         <v>-0.87769844706564</v>
       </c>
       <c r="O368" s="4" t="inlineStr">
@@ -29863,7 +29878,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G369" s="4" t="n">
+      <c r="G369" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H369" s="4" t="inlineStr">
@@ -29896,7 +29911,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N369" s="4" t="n">
+      <c r="N369" s="8" t="n">
         <v>35.7068476087747</v>
       </c>
       <c r="O369" s="4" t="inlineStr">
@@ -29942,7 +29957,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G370" s="4" t="n">
+      <c r="G370" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H370" s="4" t="inlineStr">
@@ -29975,7 +29990,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N370" s="4" t="n">
+      <c r="N370" s="8" t="n">
         <v>17.8169755565469</v>
       </c>
       <c r="O370" s="4" t="inlineStr">
@@ -30021,7 +30036,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G371" s="4" t="n">
+      <c r="G371" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H371" s="4" t="inlineStr">
@@ -30054,7 +30069,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N371" s="4" t="n">
+      <c r="N371" s="8" t="n">
         <v>101.132755331824</v>
       </c>
       <c r="O371" s="4" t="inlineStr">
@@ -30100,7 +30115,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G372" s="4" t="n">
+      <c r="G372" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H372" s="4" t="inlineStr">
@@ -30133,7 +30148,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N372" s="4" t="n">
+      <c r="N372" s="8" t="n">
         <v>41.4201088785186</v>
       </c>
       <c r="O372" s="4" t="inlineStr">
@@ -30179,7 +30194,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G373" s="4" t="n">
+      <c r="G373" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H373" s="4" t="inlineStr">
@@ -30212,7 +30227,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N373" s="4" t="n">
+      <c r="N373" s="8" t="n">
         <v>21.6148097546419</v>
       </c>
       <c r="O373" s="4" t="inlineStr">
@@ -30258,7 +30273,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G374" s="4" t="n">
+      <c r="G374" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H374" s="4" t="inlineStr">
@@ -30291,7 +30306,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N374" s="4" t="n">
+      <c r="N374" s="8" t="n">
         <v>28.3039973319823</v>
       </c>
       <c r="O374" s="4" t="inlineStr">
@@ -30337,7 +30352,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G375" s="4" t="n">
+      <c r="G375" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H375" s="4" t="inlineStr">
@@ -30370,7 +30385,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N375" s="4" t="n">
+      <c r="N375" s="8" t="n">
         <v>31.6690080487957</v>
       </c>
       <c r="O375" s="4" t="inlineStr">
@@ -30416,7 +30431,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G376" s="4" t="n">
+      <c r="G376" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H376" s="4" t="inlineStr">
@@ -30449,7 +30464,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N376" s="4" t="n">
+      <c r="N376" s="8" t="n">
         <v>62.8308497602543</v>
       </c>
       <c r="O376" s="4" t="inlineStr">
@@ -30495,7 +30510,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G377" s="4" t="n">
+      <c r="G377" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H377" s="4" t="inlineStr">
@@ -30528,7 +30543,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N377" s="4" t="n">
+      <c r="N377" s="8" t="n">
         <v>51.7661713803863</v>
       </c>
       <c r="O377" s="4" t="inlineStr">
@@ -30574,7 +30589,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G378" s="4" t="n">
+      <c r="G378" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H378" s="4" t="inlineStr">
@@ -30607,7 +30622,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N378" s="4" t="n">
+      <c r="N378" s="8" t="n">
         <v>115.644264591004</v>
       </c>
       <c r="O378" s="4" t="inlineStr">
@@ -30653,7 +30668,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G379" s="4" t="n">
+      <c r="G379" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H379" s="4" t="inlineStr">
@@ -30686,7 +30701,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N379" s="4" t="n">
+      <c r="N379" s="8" t="n">
         <v>33.9798981387027</v>
       </c>
       <c r="O379" s="4" t="inlineStr">
@@ -30732,7 +30747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G380" s="4" t="n">
+      <c r="G380" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H380" s="4" t="inlineStr">
@@ -30765,7 +30780,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N380" s="4" t="n">
+      <c r="N380" s="8" t="n">
         <v>18.6734294422431</v>
       </c>
       <c r="O380" s="4" t="inlineStr">
@@ -30811,7 +30826,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G381" s="4" t="n">
+      <c r="G381" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H381" s="4" t="inlineStr">
@@ -30844,7 +30859,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N381" s="4" t="n">
+      <c r="N381" s="8" t="n">
         <v>26.1494894419132</v>
       </c>
       <c r="O381" s="4" t="inlineStr">
@@ -30890,7 +30905,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G382" s="4" t="n">
+      <c r="G382" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H382" s="4" t="inlineStr">
@@ -30923,7 +30938,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N382" s="4" t="n">
+      <c r="N382" s="8" t="n">
         <v>29.6423626437172</v>
       </c>
       <c r="O382" s="4" t="inlineStr">
@@ -30969,7 +30984,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G383" s="4" t="n">
+      <c r="G383" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H383" s="4" t="inlineStr">
@@ -31002,7 +31017,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N383" s="4" t="n">
+      <c r="N383" s="8" t="n">
         <v>7.97560218698187</v>
       </c>
       <c r="O383" s="4" t="inlineStr">
@@ -31048,7 +31063,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G384" s="4" t="n">
+      <c r="G384" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H384" s="4" t="inlineStr">
@@ -31081,7 +31096,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N384" s="4" t="n">
+      <c r="N384" s="8" t="n">
         <v>32.8345319182831</v>
       </c>
       <c r="O384" s="4" t="inlineStr">
@@ -31127,7 +31142,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G385" s="4" t="n">
+      <c r="G385" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H385" s="4" t="inlineStr">
@@ -31160,7 +31175,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N385" s="4" t="n">
+      <c r="N385" s="8" t="n">
         <v>34.9288379544342</v>
       </c>
       <c r="O385" s="4" t="inlineStr">
@@ -31206,7 +31221,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G386" s="4" t="n">
+      <c r="G386" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H386" s="4" t="inlineStr">
@@ -31239,7 +31254,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N386" s="4" t="n">
+      <c r="N386" s="8" t="n">
         <v>34.0436148677513</v>
       </c>
       <c r="O386" s="4" t="inlineStr">
@@ -31285,7 +31300,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G387" s="4" t="n">
+      <c r="G387" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H387" s="4" t="inlineStr">
@@ -31318,7 +31333,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N387" s="4" t="n">
+      <c r="N387" s="8" t="n">
         <v>29.75501219662</v>
       </c>
       <c r="O387" s="4" t="inlineStr">
@@ -31364,7 +31379,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G388" s="4" t="n">
+      <c r="G388" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H388" s="4" t="inlineStr">
@@ -31397,7 +31412,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N388" s="4" t="n">
+      <c r="N388" s="8" t="n">
         <v>17.882509793009</v>
       </c>
       <c r="O388" s="4" t="inlineStr">
@@ -31443,7 +31458,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G389" s="4" t="n">
+      <c r="G389" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H389" s="4" t="inlineStr">
@@ -31476,7 +31491,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N389" s="4" t="n">
+      <c r="N389" s="8" t="n">
         <v>15.3925782088896</v>
       </c>
       <c r="O389" s="4" t="inlineStr">
@@ -31522,7 +31537,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G390" s="4" t="n">
+      <c r="G390" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H390" s="4" t="inlineStr">
@@ -31555,7 +31570,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N390" s="4" t="n">
+      <c r="N390" s="8" t="n">
         <v>30.2091684768406</v>
       </c>
       <c r="O390" s="4" t="inlineStr">
@@ -31601,7 +31616,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G391" s="4" t="n">
+      <c r="G391" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H391" s="4" t="inlineStr">
@@ -31634,7 +31649,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N391" s="4" t="n">
+      <c r="N391" s="8" t="n">
         <v>7.69217544074034</v>
       </c>
       <c r="O391" s="4" t="inlineStr">
@@ -31680,7 +31695,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G392" s="4" t="n">
+      <c r="G392" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H392" s="4" t="inlineStr">
@@ -31713,7 +31728,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N392" s="4" t="n">
+      <c r="N392" s="8" t="n">
         <v>46.0893567618569</v>
       </c>
       <c r="O392" s="4" t="inlineStr">
@@ -31759,7 +31774,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G393" s="4" t="n">
+      <c r="G393" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H393" s="4" t="inlineStr">
@@ -31792,7 +31807,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N393" s="4" t="n">
+      <c r="N393" s="8" t="n">
         <v>28.2163432253321</v>
       </c>
       <c r="O393" s="4" t="inlineStr">
@@ -31838,7 +31853,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G394" s="4" t="n">
+      <c r="G394" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H394" s="4" t="inlineStr">
@@ -31871,7 +31886,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N394" s="4" t="n">
+      <c r="N394" s="8" t="n">
         <v>20.5919077245585</v>
       </c>
       <c r="O394" s="4" t="inlineStr">
@@ -31917,7 +31932,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G395" s="4" t="n">
+      <c r="G395" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H395" s="4" t="inlineStr">
@@ -31950,7 +31965,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N395" s="4" t="n">
+      <c r="N395" s="8" t="n">
         <v>39.2264371875174</v>
       </c>
       <c r="O395" s="4" t="inlineStr">
@@ -31996,7 +32011,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G396" s="4" t="n">
+      <c r="G396" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H396" s="4" t="inlineStr">
@@ -32029,7 +32044,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N396" s="4" t="n">
+      <c r="N396" s="8" t="n">
         <v>105.042765502495</v>
       </c>
       <c r="O396" s="4" t="inlineStr">
@@ -32075,7 +32090,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G397" s="4" t="n">
+      <c r="G397" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H397" s="4" t="inlineStr">
@@ -32108,7 +32123,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N397" s="4" t="n">
+      <c r="N397" s="8" t="n">
         <v>134.908705496941</v>
       </c>
       <c r="O397" s="4" t="inlineStr">
@@ -32154,7 +32169,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G398" s="4" t="n">
+      <c r="G398" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H398" s="4" t="inlineStr">
@@ -32187,7 +32202,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N398" s="4" t="n">
+      <c r="N398" s="8" t="n">
         <v>308.600121728545</v>
       </c>
       <c r="O398" s="4" t="inlineStr">
@@ -32233,7 +32248,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G399" s="4" t="n">
+      <c r="G399" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H399" s="4" t="inlineStr">
@@ -32266,7 +32281,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N399" s="4" t="n">
+      <c r="N399" s="8" t="n">
         <v>1049.87777840941</v>
       </c>
       <c r="O399" s="4" t="inlineStr">
@@ -32312,7 +32327,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G400" s="4" t="n">
+      <c r="G400" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H400" s="4" t="inlineStr">
@@ -32345,7 +32360,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N400" s="4" t="n">
+      <c r="N400" s="8" t="n">
         <v>225652.234993614</v>
       </c>
       <c r="O400" s="4" t="inlineStr">
@@ -32391,7 +32406,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G401" s="4" t="n">
+      <c r="G401" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H401" s="4" t="inlineStr">
@@ -32424,7 +32439,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N401" s="4" t="n">
+      <c r="N401" s="8" t="n">
         <v>21909.3426680117</v>
       </c>
       <c r="O401" s="4" t="inlineStr">
@@ -32470,7 +32485,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G402" s="4" t="n">
+      <c r="G402" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H402" s="4" t="inlineStr">
@@ -32503,7 +32518,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N402" s="4" t="n">
+      <c r="N402" s="8" t="n">
         <v>1885.46577647144</v>
       </c>
       <c r="O402" s="4" t="inlineStr">
@@ -32549,7 +32564,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G403" s="4" t="n">
+      <c r="G403" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H403" s="4" t="inlineStr">
@@ -32582,7 +32597,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N403" s="4" t="n">
+      <c r="N403" s="8" t="n">
         <v>1212.84660038412</v>
       </c>
       <c r="O403" s="4" t="inlineStr">
@@ -32628,7 +32643,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G404" s="4" t="n">
+      <c r="G404" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H404" s="4" t="inlineStr">
@@ -32661,7 +32676,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N404" s="4" t="n">
+      <c r="N404" s="8" t="n">
         <v>210.806068385812</v>
       </c>
       <c r="O404" s="4" t="inlineStr">
@@ -32707,7 +32722,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G405" s="4" t="n">
+      <c r="G405" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H405" s="4" t="inlineStr">
@@ -32740,7 +32755,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N405" s="4" t="n">
+      <c r="N405" s="8" t="n">
         <v>367.798078256365</v>
       </c>
       <c r="O405" s="4" t="inlineStr">
@@ -32786,7 +32801,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G406" s="4" t="n">
+      <c r="G406" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H406" s="4" t="inlineStr">
@@ -32819,7 +32834,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N406" s="4" t="n">
+      <c r="N406" s="8" t="n">
         <v>55.4481074808972</v>
       </c>
       <c r="O406" s="4" t="inlineStr">
@@ -32865,7 +32880,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G407" s="4" t="n">
+      <c r="G407" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H407" s="4" t="inlineStr">
@@ -32898,7 +32913,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N407" s="4" t="n">
+      <c r="N407" s="8" t="n">
         <v>227.093064600296</v>
       </c>
       <c r="O407" s="4" t="inlineStr">
@@ -32944,7 +32959,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G408" s="4" t="n">
+      <c r="G408" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H408" s="4" t="inlineStr">
@@ -32977,7 +32992,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N408" s="4" t="n">
+      <c r="N408" s="8" t="n">
         <v>0.00334958333233334</v>
       </c>
       <c r="O408" s="4" t="inlineStr">
@@ -33023,7 +33038,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G409" s="4" t="n">
+      <c r="G409" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H409" s="4" t="inlineStr">
@@ -33056,7 +33071,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N409" s="4" t="n">
+      <c r="N409" s="8" t="n">
         <v>0.00334983333233333</v>
       </c>
       <c r="O409" s="4" t="inlineStr">
@@ -33102,7 +33117,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G410" s="4" t="n">
+      <c r="G410" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H410" s="4" t="inlineStr">
@@ -33135,7 +33150,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N410" s="4" t="n">
+      <c r="N410" s="8" t="n">
         <v>0.00334966666566667</v>
       </c>
       <c r="O410" s="4" t="inlineStr">
@@ -33181,7 +33196,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G411" s="4" t="n">
+      <c r="G411" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H411" s="4" t="inlineStr">
@@ -33214,7 +33229,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N411" s="4" t="n">
+      <c r="N411" s="8" t="n">
         <v>0.00334966666566666</v>
       </c>
       <c r="O411" s="4" t="inlineStr">
@@ -33260,7 +33275,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G412" s="4" t="n">
+      <c r="G412" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H412" s="4" t="inlineStr">
@@ -33293,7 +33308,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N412" s="4" t="n">
+      <c r="N412" s="8" t="n">
         <v>0.00435</v>
       </c>
       <c r="O412" s="4" t="inlineStr">
@@ -33339,7 +33354,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G413" s="4" t="n">
+      <c r="G413" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H413" s="4" t="inlineStr">
@@ -33372,7 +33387,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N413" s="4" t="n">
+      <c r="N413" s="8" t="n">
         <v>0.0044</v>
       </c>
       <c r="O413" s="4" t="inlineStr">
@@ -33418,7 +33433,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G414" s="4" t="n">
+      <c r="G414" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H414" s="4" t="inlineStr">
@@ -33451,7 +33466,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N414" s="4" t="n">
+      <c r="N414" s="8" t="n">
         <v>0.0044</v>
       </c>
       <c r="O414" s="4" t="inlineStr">
@@ -33497,7 +33512,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G415" s="4" t="n">
+      <c r="G415" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H415" s="4" t="inlineStr">
@@ -33530,7 +33545,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N415" s="4" t="n">
+      <c r="N415" s="8" t="n">
         <v>0.0044</v>
       </c>
       <c r="O415" s="4" t="inlineStr">
@@ -33576,7 +33591,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G416" s="4" t="n">
+      <c r="G416" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H416" s="4" t="inlineStr">
@@ -33609,7 +33624,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N416" s="4" t="n">
+      <c r="N416" s="8" t="n">
         <v>0.0044</v>
       </c>
       <c r="O416" s="4" t="inlineStr">
@@ -33655,7 +33670,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G417" s="4" t="n">
+      <c r="G417" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H417" s="4" t="inlineStr">
@@ -33688,7 +33703,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N417" s="4" t="n">
+      <c r="N417" s="8" t="n">
         <v>0.0044</v>
       </c>
       <c r="O417" s="4" t="inlineStr">
@@ -33734,7 +33749,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G418" s="4" t="n">
+      <c r="G418" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H418" s="4" t="inlineStr">
@@ -33767,7 +33782,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N418" s="4" t="n">
+      <c r="N418" s="8" t="n">
         <v>0.0044</v>
       </c>
       <c r="O418" s="4" t="inlineStr">
@@ -33813,7 +33828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G419" s="4" t="n">
+      <c r="G419" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H419" s="4" t="inlineStr">
@@ -33846,7 +33861,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N419" s="4" t="n">
+      <c r="N419" s="8" t="n">
         <v>0.0044</v>
       </c>
       <c r="O419" s="4" t="inlineStr">
@@ -33892,7 +33907,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G420" s="4" t="n">
+      <c r="G420" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H420" s="4" t="inlineStr">
@@ -33925,7 +33940,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N420" s="4" t="n">
+      <c r="N420" s="8" t="n">
         <v>0.0043</v>
       </c>
       <c r="O420" s="4" t="inlineStr">
@@ -33971,7 +33986,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G421" s="4" t="n">
+      <c r="G421" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H421" s="4" t="inlineStr">
@@ -34004,7 +34019,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N421" s="4" t="n">
+      <c r="N421" s="8" t="n">
         <v>0.0043</v>
       </c>
       <c r="O421" s="4" t="inlineStr">
@@ -34050,7 +34065,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G422" s="4" t="n">
+      <c r="G422" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H422" s="4" t="inlineStr">
@@ -34083,7 +34098,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N422" s="4" t="n">
+      <c r="N422" s="8" t="n">
         <v>0.0043</v>
       </c>
       <c r="O422" s="4" t="inlineStr">
@@ -34129,7 +34144,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G423" s="4" t="n">
+      <c r="G423" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H423" s="4" t="inlineStr">
@@ -34162,7 +34177,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N423" s="4" t="n">
+      <c r="N423" s="8" t="n">
         <v>0.0043</v>
       </c>
       <c r="O423" s="4" t="inlineStr">
@@ -34208,7 +34223,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G424" s="4" t="n">
+      <c r="G424" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H424" s="4" t="inlineStr">
@@ -34241,7 +34256,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N424" s="4" t="n">
+      <c r="N424" s="8" t="n">
         <v>0.0043</v>
       </c>
       <c r="O424" s="4" t="inlineStr">
@@ -34287,7 +34302,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G425" s="4" t="n">
+      <c r="G425" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H425" s="4" t="inlineStr">
@@ -34320,7 +34335,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N425" s="4" t="n">
+      <c r="N425" s="8" t="n">
         <v>0.0043</v>
       </c>
       <c r="O425" s="4" t="inlineStr">
@@ -34366,7 +34381,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G426" s="4" t="n">
+      <c r="G426" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H426" s="4" t="inlineStr">
@@ -34399,7 +34414,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N426" s="4" t="n">
+      <c r="N426" s="8" t="n">
         <v>0.0043</v>
       </c>
       <c r="O426" s="4" t="inlineStr">
@@ -34445,7 +34460,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G427" s="4" t="n">
+      <c r="G427" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H427" s="4" t="inlineStr">
@@ -34478,7 +34493,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N427" s="4" t="n">
+      <c r="N427" s="8" t="n">
         <v>0.0043</v>
       </c>
       <c r="O427" s="4" t="inlineStr">
@@ -34524,7 +34539,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G428" s="4" t="n">
+      <c r="G428" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H428" s="4" t="inlineStr">
@@ -34557,7 +34572,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N428" s="4" t="n">
+      <c r="N428" s="8" t="n">
         <v>0.0043</v>
       </c>
       <c r="O428" s="4" t="inlineStr">
@@ -34603,7 +34618,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G429" s="4" t="n">
+      <c r="G429" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H429" s="4" t="inlineStr">
@@ -34636,7 +34651,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N429" s="4" t="n">
+      <c r="N429" s="8" t="n">
         <v>0.0043</v>
       </c>
       <c r="O429" s="4" t="inlineStr">
@@ -34682,7 +34697,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G430" s="4" t="n">
+      <c r="G430" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H430" s="4" t="inlineStr">
@@ -34715,7 +34730,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N430" s="4" t="n">
+      <c r="N430" s="8" t="n">
         <v>0.0043</v>
       </c>
       <c r="O430" s="4" t="inlineStr">
@@ -34761,7 +34776,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G431" s="4" t="n">
+      <c r="G431" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H431" s="4" t="inlineStr">
@@ -34794,7 +34809,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N431" s="4" t="n">
+      <c r="N431" s="8" t="n">
         <v>0.0043</v>
       </c>
       <c r="O431" s="4" t="inlineStr">
@@ -34840,7 +34855,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G432" s="4" t="n">
+      <c r="G432" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H432" s="4" t="inlineStr">
@@ -34873,7 +34888,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N432" s="4" t="n">
+      <c r="N432" s="8" t="n">
         <v>0.00701666666666667</v>
       </c>
       <c r="O432" s="4" t="inlineStr">
@@ -34919,7 +34934,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G433" s="4" t="n">
+      <c r="G433" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H433" s="4" t="inlineStr">
@@ -34952,7 +34967,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N433" s="4" t="n">
+      <c r="N433" s="8" t="n">
         <v>0.0075</v>
       </c>
       <c r="O433" s="4" t="inlineStr">
@@ -34998,7 +35013,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G434" s="4" t="n">
+      <c r="G434" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H434" s="4" t="inlineStr">
@@ -35031,7 +35046,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N434" s="4" t="n">
+      <c r="N434" s="8" t="n">
         <v>0.00808333333333333</v>
       </c>
       <c r="O434" s="4" t="inlineStr">
@@ -35077,7 +35092,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G435" s="4" t="n">
+      <c r="G435" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H435" s="4" t="inlineStr">
@@ -35110,7 +35125,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N435" s="4" t="n">
+      <c r="N435" s="8" t="n">
         <v>0.0145</v>
       </c>
       <c r="O435" s="4" t="inlineStr">
@@ -35156,7 +35171,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G436" s="4" t="n">
+      <c r="G436" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H436" s="4" t="inlineStr">
@@ -35189,7 +35204,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N436" s="4" t="n">
+      <c r="N436" s="8" t="n">
         <v>0.0145</v>
       </c>
       <c r="O436" s="4" t="inlineStr">
@@ -35235,7 +35250,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G437" s="4" t="n">
+      <c r="G437" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H437" s="4" t="inlineStr">
@@ -35268,7 +35283,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N437" s="4" t="n">
+      <c r="N437" s="8" t="n">
         <v>0.0346916666666667</v>
       </c>
       <c r="O437" s="4" t="inlineStr">
@@ -35314,7 +35329,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G438" s="4" t="n">
+      <c r="G438" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H438" s="4" t="inlineStr">
@@ -35347,7 +35362,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N438" s="4" t="n">
+      <c r="N438" s="8" t="n">
         <v>0.0468916666666667</v>
       </c>
       <c r="O438" s="4" t="inlineStr">
@@ -35393,7 +35408,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G439" s="4" t="n">
+      <c r="G439" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H439" s="4" t="inlineStr">
@@ -35426,7 +35441,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N439" s="4" t="n">
+      <c r="N439" s="8" t="n">
         <v>0.056825</v>
       </c>
       <c r="O439" s="4" t="inlineStr">
@@ -35472,7 +35487,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G440" s="4" t="n">
+      <c r="G440" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H440" s="4" t="inlineStr">
@@ -35505,7 +35520,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N440" s="4" t="n">
+      <c r="N440" s="8" t="n">
         <v>0.0683833333333333</v>
       </c>
       <c r="O440" s="4" t="inlineStr">
@@ -35551,7 +35566,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G441" s="4" t="n">
+      <c r="G441" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H441" s="4" t="inlineStr">
@@ -35584,7 +35599,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N441" s="4" t="n">
+      <c r="N441" s="8" t="n">
         <v>0.0908416666666667</v>
       </c>
       <c r="O441" s="4" t="inlineStr">
@@ -35630,7 +35645,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G442" s="4" t="n">
+      <c r="G442" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H442" s="4" t="inlineStr">
@@ -35663,7 +35678,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N442" s="4" t="n">
+      <c r="N442" s="8" t="n">
         <v>0.146858333333333</v>
       </c>
       <c r="O442" s="4" t="inlineStr">
@@ -35709,7 +35724,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G443" s="4" t="n">
+      <c r="G443" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H443" s="4" t="inlineStr">
@@ -35742,7 +35757,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N443" s="4" t="n">
+      <c r="N443" s="8" t="n">
         <v>0.176841666666667</v>
       </c>
       <c r="O443" s="4" t="inlineStr">
@@ -35788,7 +35803,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G444" s="4" t="n">
+      <c r="G444" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H444" s="4" t="inlineStr">
@@ -35821,7 +35836,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N444" s="4" t="n">
+      <c r="N444" s="8" t="n">
         <v>0.41735</v>
       </c>
       <c r="O444" s="4" t="inlineStr">
@@ -35867,7 +35882,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G445" s="4" t="n">
+      <c r="G445" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H445" s="4" t="inlineStr">
@@ -35900,7 +35915,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N445" s="4" t="n">
+      <c r="N445" s="8" t="n">
         <v>0.488633333333333</v>
       </c>
       <c r="O445" s="4" t="inlineStr">
@@ -35946,7 +35961,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G446" s="4" t="n">
+      <c r="G446" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H446" s="4" t="inlineStr">
@@ -35979,7 +35994,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N446" s="4" t="n">
+      <c r="N446" s="8" t="n">
         <v>0.547566666666667</v>
       </c>
       <c r="O446" s="4" t="inlineStr">
@@ -36025,7 +36040,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G447" s="4" t="n">
+      <c r="G447" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H447" s="4" t="inlineStr">
@@ -36058,7 +36073,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N447" s="4" t="n">
+      <c r="N447" s="8" t="n">
         <v>0.605725</v>
       </c>
       <c r="O447" s="4" t="inlineStr">
@@ -36104,7 +36119,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G448" s="4" t="n">
+      <c r="G448" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H448" s="4" t="inlineStr">
@@ -36137,7 +36152,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N448" s="4" t="n">
+      <c r="N448" s="8" t="n">
         <v>0.6799666666666671</v>
       </c>
       <c r="O448" s="4" t="inlineStr">
@@ -36183,7 +36198,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G449" s="4" t="n">
+      <c r="G449" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H449" s="4" t="inlineStr">
@@ -36216,7 +36231,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N449" s="4" t="n">
+      <c r="N449" s="8" t="n">
         <v>0.723658333333334</v>
       </c>
       <c r="O449" s="4" t="inlineStr">
@@ -36262,7 +36277,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G450" s="4" t="n">
+      <c r="G450" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H450" s="4" t="inlineStr">
@@ -36295,7 +36310,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N450" s="4" t="n">
+      <c r="N450" s="8" t="n">
         <v>1.16095</v>
       </c>
       <c r="O450" s="4" t="inlineStr">
@@ -36341,7 +36356,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G451" s="4" t="n">
+      <c r="G451" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H451" s="4" t="inlineStr">
@@ -36374,7 +36389,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N451" s="4" t="n">
+      <c r="N451" s="8" t="n">
         <v>1.60695833333333</v>
       </c>
       <c r="O451" s="4" t="inlineStr">
@@ -36420,7 +36435,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G452" s="4" t="n">
+      <c r="G452" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H452" s="4" t="inlineStr">
@@ -36453,7 +36468,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N452" s="4" t="n">
+      <c r="N452" s="8" t="n">
         <v>1.89133333333333</v>
       </c>
       <c r="O452" s="4" t="inlineStr">
@@ -36499,7 +36514,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G453" s="4" t="n">
+      <c r="G453" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H453" s="4" t="inlineStr">
@@ -36532,7 +36547,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N453" s="4" t="n">
+      <c r="N453" s="8" t="n">
         <v>2.08975</v>
       </c>
       <c r="O453" s="4" t="inlineStr">
@@ -36578,7 +36593,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G454" s="4" t="n">
+      <c r="G454" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H454" s="4" t="inlineStr">
@@ -36611,7 +36626,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N454" s="4" t="n">
+      <c r="N454" s="8" t="n">
         <v>2.147</v>
       </c>
       <c r="O454" s="4" t="inlineStr">
@@ -36657,7 +36672,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G455" s="4" t="n">
+      <c r="G455" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H455" s="4" t="inlineStr">
@@ -36690,7 +36705,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N455" s="4" t="n">
+      <c r="N455" s="8" t="n">
         <v>2.147</v>
       </c>
       <c r="O455" s="4" t="inlineStr">
@@ -36736,7 +36751,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G456" s="4" t="n">
+      <c r="G456" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H456" s="4" t="inlineStr">
@@ -36769,7 +36784,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N456" s="4" t="n">
+      <c r="N456" s="8" t="n">
         <v>2.147</v>
       </c>
       <c r="O456" s="4" t="inlineStr">
@@ -36815,7 +36830,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G457" s="4" t="n">
+      <c r="G457" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H457" s="4" t="inlineStr">
@@ -36848,7 +36863,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N457" s="4" t="n">
+      <c r="N457" s="8" t="n">
         <v>2.147</v>
       </c>
       <c r="O457" s="4" t="inlineStr">
@@ -36894,7 +36909,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G458" s="4" t="n">
+      <c r="G458" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H458" s="4" t="inlineStr">
@@ -36927,7 +36942,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N458" s="4" t="n">
+      <c r="N458" s="8" t="n">
         <v>2.58206031746032</v>
       </c>
       <c r="O458" s="4" t="inlineStr">
@@ -36973,7 +36988,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G459" s="4" t="n">
+      <c r="G459" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H459" s="4" t="inlineStr">
@@ -37006,7 +37021,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N459" s="4" t="n">
+      <c r="N459" s="8" t="n">
         <v>4.2893</v>
       </c>
       <c r="O459" s="4" t="inlineStr">
@@ -37052,7 +37067,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G460" s="4" t="n">
+      <c r="G460" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H460" s="4" t="inlineStr">
@@ -37085,7 +37100,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N460" s="4" t="n">
+      <c r="N460" s="8" t="n">
         <v>4.2893</v>
       </c>
       <c r="O460" s="4" t="inlineStr">
@@ -37131,7 +37146,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G461" s="4" t="n">
+      <c r="G461" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H461" s="4" t="inlineStr">
@@ -37164,7 +37179,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N461" s="4" t="n">
+      <c r="N461" s="8" t="n">
         <v>6.04796184166667</v>
       </c>
       <c r="O461" s="4" t="inlineStr">
@@ -37210,7 +37225,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G462" s="4" t="n">
+      <c r="G462" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H462" s="4" t="inlineStr">
@@ -37243,7 +37258,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N462" s="4" t="n">
+      <c r="N462" s="8" t="n">
         <v>6.2842</v>
       </c>
       <c r="O462" s="4" t="inlineStr">
@@ -37289,7 +37304,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G463" s="4" t="n">
+      <c r="G463" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H463" s="4" t="inlineStr">
@@ -37322,7 +37337,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N463" s="4" t="n">
+      <c r="N463" s="8" t="n">
         <v>6.2842</v>
       </c>
       <c r="O463" s="4" t="inlineStr">
@@ -37368,7 +37383,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G464" s="4" t="n">
+      <c r="G464" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H464" s="4" t="inlineStr">
@@ -37401,7 +37416,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N464" s="4" t="n">
+      <c r="N464" s="8" t="n">
         <v>9.257344444441671</v>
       </c>
       <c r="O464" s="4" t="inlineStr">
@@ -37447,7 +37462,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G465" s="4" t="n">
+      <c r="G465" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H465" s="4" t="inlineStr">
@@ -37480,7 +37495,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N465" s="4" t="n">
+      <c r="N465" s="8" t="n">
         <v>9.975</v>
       </c>
       <c r="O465" s="4" t="inlineStr">
@@ -37526,7 +37541,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G466" s="4" t="n">
+      <c r="G466" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H466" s="4" t="inlineStr">
@@ -37603,7 +37618,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G467" s="4" t="n">
+      <c r="G467" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H467" s="4" t="inlineStr">
@@ -37680,7 +37695,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G468" s="4" t="n">
+      <c r="G468" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H468" s="4" t="inlineStr">
@@ -37757,7 +37772,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G469" s="4" t="n">
+      <c r="G469" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H469" s="4" t="inlineStr">
@@ -37834,7 +37849,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G470" s="4" t="n">
+      <c r="G470" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H470" s="4" t="inlineStr">
@@ -37911,7 +37926,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G471" s="4" t="n">
+      <c r="G471" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H471" s="4" t="inlineStr">
@@ -37988,7 +38003,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G472" s="4" t="n">
+      <c r="G472" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H472" s="4" t="inlineStr">
@@ -38065,7 +38080,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G473" s="4" t="n">
+      <c r="G473" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H473" s="4" t="inlineStr">
@@ -38201,7 +38216,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>7</v>
       </c>
     </row>
@@ -38211,7 +38226,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>467</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q470"/>
+  <dimension ref="A1:Q469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16193,14 +16193,10 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q205" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -16274,14 +16270,10 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q206" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -16355,14 +16347,10 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q207" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
@@ -16436,14 +16424,10 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q208" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -16517,14 +16501,10 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q209" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -16598,14 +16578,10 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q210" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q210" s="4" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -16679,14 +16655,10 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q211" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q211" s="4" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -16760,14 +16732,10 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q212" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -16841,14 +16809,10 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q213" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -16922,14 +16886,10 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q214" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -17003,14 +16963,10 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q215" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
@@ -17084,14 +17040,10 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q216" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -17165,14 +17117,10 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q217" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q217" s="4" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
@@ -17246,14 +17194,10 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q218" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q218" s="4" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -17327,14 +17271,10 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q219" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
@@ -17408,14 +17348,10 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q220" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
@@ -17489,14 +17425,10 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q221" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
@@ -17570,14 +17502,10 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q222" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
@@ -17651,14 +17579,10 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q223" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
@@ -17732,14 +17656,10 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q224" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q224" s="4" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
@@ -17813,14 +17733,10 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q225" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q225" s="4" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
@@ -17894,14 +17810,10 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q226" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
@@ -17975,14 +17887,10 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q227" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
@@ -18056,14 +17964,10 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q228" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
@@ -18137,14 +18041,10 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q229" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
@@ -18218,14 +18118,10 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q230" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
@@ -18299,14 +18195,10 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q231" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q231" s="4" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
@@ -18380,14 +18272,10 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q232" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q232" s="4" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
@@ -18461,14 +18349,10 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q233" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
@@ -18542,14 +18426,10 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q234" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
@@ -18623,14 +18503,10 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q235" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
@@ -18704,14 +18580,10 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q236" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
@@ -18785,14 +18657,10 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q237" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
@@ -18866,14 +18734,10 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q238" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q238" s="4" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
@@ -18947,14 +18811,10 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q239" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q239" s="4" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
@@ -19028,14 +18888,10 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q240" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
@@ -19109,14 +18965,10 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q241" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
@@ -19190,14 +19042,10 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q242" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
@@ -19271,14 +19119,10 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q243" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
@@ -19352,14 +19196,10 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q244" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
@@ -19433,14 +19273,10 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q245" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q245" s="4" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
@@ -19514,14 +19350,10 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q246" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q246" s="4" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
@@ -19595,14 +19427,10 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q247" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
@@ -19676,14 +19504,10 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q248" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q248" s="4" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
@@ -19757,14 +19581,10 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q249" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q249" s="4" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
@@ -19838,14 +19658,10 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q250" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q250" s="4" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
@@ -19919,14 +19735,10 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q251" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
@@ -20000,14 +19812,10 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q252" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q252" s="4" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
@@ -20081,14 +19889,10 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q253" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q253" s="4" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
@@ -20154,7 +19958,9 @@
           <t>Inflación anual de precios al consumidor</t>
         </is>
       </c>
-      <c r="N254" s="4" t="n"/>
+      <c r="N254" s="6" t="n">
+        <v>27.080941446613</v>
+      </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20162,14 +19968,10 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q254" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q254" s="4" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
@@ -20235,7 +20037,9 @@
           <t>Inflación anual de precios al consumidor</t>
         </is>
       </c>
-      <c r="N255" s="4" t="n"/>
+      <c r="N255" s="6" t="n">
+        <v>28.1874647092039</v>
+      </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20243,14 +20047,10 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q255" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q255" s="4" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
@@ -20316,7 +20116,9 @@
           <t>Inflación anual de precios al consumidor</t>
         </is>
       </c>
-      <c r="N256" s="4" t="n"/>
+      <c r="N256" s="6" t="n">
+        <v>26.0902123160959</v>
+      </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20324,14 +20126,10 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q256" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q256" s="4" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
@@ -20397,7 +20195,9 @@
           <t>Inflación anual de precios al consumidor</t>
         </is>
       </c>
-      <c r="N257" s="4" t="n"/>
+      <c r="N257" s="6" t="n">
+        <v>21.0689956331876</v>
+      </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20405,14 +20205,10 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q257" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q257" s="4" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
@@ -20478,7 +20274,9 @@
           <t>Inflación anual de precios al consumidor</t>
         </is>
       </c>
-      <c r="N258" s="4" t="n"/>
+      <c r="N258" s="6" t="n">
+        <v>40.6394275161589</v>
+      </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20486,14 +20284,10 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q258" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q258" s="4" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
@@ -20559,7 +20353,9 @@
           <t>Inflación anual de precios al consumidor</t>
         </is>
       </c>
-      <c r="N259" s="4" t="n"/>
+      <c r="N259" s="6" t="n">
+        <v>62.1686499794829</v>
+      </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20567,14 +20363,10 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q259" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q259" s="4" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
@@ -20640,7 +20432,9 @@
           <t>Inflación anual de precios al consumidor</t>
         </is>
       </c>
-      <c r="N260" s="4" t="n"/>
+      <c r="N260" s="6" t="n">
+        <v>121.738085297503</v>
+      </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20648,14 +20442,10 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q260" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q260" s="4" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
@@ -20721,7 +20511,9 @@
           <t>Inflación anual de precios al consumidor</t>
         </is>
       </c>
-      <c r="N261" s="4" t="n"/>
+      <c r="N261" s="6" t="n">
+        <v>254.948534781816</v>
+      </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20729,14 +20521,10 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q261" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
@@ -20810,14 +20598,10 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q262" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q262" s="4" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
@@ -20891,14 +20675,10 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q263" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q263" s="4" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
@@ -20972,14 +20752,10 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q264" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q264" s="4" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
@@ -21053,14 +20829,10 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q265" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q265" s="4" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
@@ -21134,14 +20906,10 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q266" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q266" s="4" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
@@ -21215,14 +20983,10 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q267" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q267" s="4" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
@@ -21296,14 +21060,10 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q268" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q268" s="4" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
@@ -21377,14 +21137,10 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q269" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q269" s="4" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
@@ -21458,14 +21214,10 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q270" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q270" s="4" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
@@ -21499,7 +21251,7 @@
         </is>
       </c>
       <c r="G271" s="5" t="n">
-        <v>2026</v>
+        <v>1960</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
@@ -21513,22 +21265,22 @@
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
-          <t>Inflación</t>
+          <t>Sistema financiero</t>
         </is>
       </c>
       <c r="K271" s="4" t="inlineStr">
         <is>
-          <t>inflacion</t>
+          <t>sistema_financiero</t>
         </is>
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>FP.CPI.TOTL.ZG</t>
+          <t>FR.INR.RINR</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
         <is>
-          <t>Inflación anual de precios al consumidor</t>
+          <t>Tipo de interés real</t>
         </is>
       </c>
       <c r="N271" s="4" t="n"/>
@@ -21539,14 +21291,10 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q271" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q271" s="4" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
@@ -21580,7 +21328,7 @@
         </is>
       </c>
       <c r="G272" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
@@ -21620,14 +21368,10 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q272" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q272" s="4" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
@@ -21661,7 +21405,7 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
@@ -21701,14 +21445,10 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q273" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q273" s="4" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
@@ -21742,7 +21482,7 @@
         </is>
       </c>
       <c r="G274" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
@@ -21782,14 +21522,10 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q274" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q274" s="4" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
@@ -21823,7 +21559,7 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
@@ -21863,14 +21599,10 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q275" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q275" s="4" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
@@ -21904,7 +21636,7 @@
         </is>
       </c>
       <c r="G276" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
@@ -21944,14 +21676,10 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q276" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q276" s="4" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
@@ -21985,7 +21713,7 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -22025,14 +21753,10 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q277" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q277" s="4" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
@@ -22066,7 +21790,7 @@
         </is>
       </c>
       <c r="G278" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
@@ -22106,14 +21830,10 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q278" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q278" s="4" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
@@ -22147,7 +21867,7 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
@@ -22187,14 +21907,10 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q279" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q279" s="4" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
@@ -22228,7 +21944,7 @@
         </is>
       </c>
       <c r="G280" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
@@ -22268,14 +21984,10 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q280" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q280" s="4" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
@@ -22309,7 +22021,7 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
@@ -22349,14 +22061,10 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q281" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q281" s="4" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
@@ -22390,7 +22098,7 @@
         </is>
       </c>
       <c r="G282" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
@@ -22430,14 +22138,10 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q282" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q282" s="4" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
@@ -22471,7 +22175,7 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
@@ -22511,14 +22215,10 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q283" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q283" s="4" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
@@ -22552,7 +22252,7 @@
         </is>
       </c>
       <c r="G284" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
@@ -22592,14 +22292,10 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q284" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q284" s="4" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
@@ -22633,7 +22329,7 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
@@ -22673,14 +22369,10 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q285" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q285" s="4" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
@@ -22714,7 +22406,7 @@
         </is>
       </c>
       <c r="G286" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
@@ -22754,14 +22446,10 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q286" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q286" s="4" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
@@ -22795,7 +22483,7 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -22835,14 +22523,10 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q287" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q287" s="4" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
@@ -22876,7 +22560,7 @@
         </is>
       </c>
       <c r="G288" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
@@ -22916,14 +22600,10 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q288" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q288" s="4" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
@@ -22957,7 +22637,7 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -22997,14 +22677,10 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q289" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q289" s="4" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
@@ -23038,7 +22714,7 @@
         </is>
       </c>
       <c r="G290" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -23078,14 +22754,10 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q290" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q290" s="4" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
@@ -23119,7 +22791,7 @@
         </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
@@ -23159,14 +22831,10 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q291" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q291" s="4" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
@@ -23200,7 +22868,7 @@
         </is>
       </c>
       <c r="G292" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
@@ -23240,14 +22908,10 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q292" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q292" s="4" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
@@ -23281,7 +22945,7 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
@@ -23321,14 +22985,10 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q293" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q293" s="4" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
@@ -23362,7 +23022,7 @@
         </is>
       </c>
       <c r="G294" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
@@ -23402,14 +23062,10 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q294" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q294" s="4" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
@@ -23443,7 +23099,7 @@
         </is>
       </c>
       <c r="G295" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
@@ -23475,7 +23131,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N295" s="4" t="n"/>
+      <c r="N295" s="6" t="n">
+        <v>-20.3105843528903</v>
+      </c>
       <c r="O295" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23483,14 +23141,10 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q295" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q295" s="4" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
@@ -23524,7 +23178,7 @@
         </is>
       </c>
       <c r="G296" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
@@ -23556,7 +23210,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N296" s="4" t="n"/>
+      <c r="N296" s="6" t="n">
+        <v>-0.53261518686187</v>
+      </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23564,14 +23220,10 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q296" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q296" s="4" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
@@ -23605,7 +23257,7 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -23637,7 +23289,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N297" s="4" t="n"/>
+      <c r="N297" s="6" t="n">
+        <v>9.44728377673056</v>
+      </c>
       <c r="O297" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23645,14 +23299,10 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q297" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q297" s="4" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
@@ -23686,7 +23336,7 @@
         </is>
       </c>
       <c r="G298" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
@@ -23718,7 +23368,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N298" s="4" t="n"/>
+      <c r="N298" s="6" t="n">
+        <v>-20.0691279931751</v>
+      </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23726,14 +23378,10 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q298" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q298" s="4" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
@@ -23767,7 +23415,7 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -23799,7 +23447,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N299" s="4" t="n"/>
+      <c r="N299" s="6" t="n">
+        <v>-7.91012968421851</v>
+      </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23807,14 +23457,10 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q299" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q299" s="4" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
@@ -23848,7 +23494,7 @@
         </is>
       </c>
       <c r="G300" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
@@ -23880,7 +23526,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N300" s="4" t="n"/>
+      <c r="N300" s="6" t="n">
+        <v>-39.0961955461174</v>
+      </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23888,14 +23536,10 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q300" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q300" s="4" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
@@ -23929,7 +23573,7 @@
         </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -23961,7 +23605,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N301" s="4" t="n"/>
+      <c r="N301" s="6" t="n">
+        <v>-4.16379414395032</v>
+      </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23969,14 +23615,10 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q301" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q301" s="4" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
@@ -24010,7 +23652,7 @@
         </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -24042,7 +23684,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N302" s="4" t="n"/>
+      <c r="N302" s="6" t="n">
+        <v>12.7850576834027</v>
+      </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24050,14 +23694,10 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q302" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q302" s="4" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
@@ -24091,7 +23731,7 @@
         </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -24123,7 +23763,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N303" s="4" t="n"/>
+      <c r="N303" s="6" t="n">
+        <v>10.1505042234342</v>
+      </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24131,14 +23773,10 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q303" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q303" s="4" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
@@ -24172,7 +23810,7 @@
         </is>
       </c>
       <c r="G304" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -24204,7 +23842,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N304" s="4" t="n"/>
+      <c r="N304" s="6" t="n">
+        <v>21.4421442344337</v>
+      </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24212,14 +23852,10 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q304" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q304" s="4" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
@@ -24253,7 +23889,7 @@
         </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -24285,7 +23921,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N305" s="4" t="n"/>
+      <c r="N305" s="6" t="n">
+        <v>-5.02106927052955</v>
+      </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24293,14 +23931,10 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q305" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q305" s="4" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
@@ -24334,7 +23968,7 @@
         </is>
       </c>
       <c r="G306" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -24366,7 +24000,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N306" s="4" t="n"/>
+      <c r="N306" s="6" t="n">
+        <v>-7.92139948209389</v>
+      </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24374,14 +24010,10 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q306" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q306" s="4" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
@@ -24415,7 +24047,7 @@
         </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -24447,7 +24079,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N307" s="4" t="n"/>
+      <c r="N307" s="6" t="n">
+        <v>-35.3503170614123</v>
+      </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24455,14 +24089,10 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q307" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q307" s="4" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
@@ -24496,7 +24126,7 @@
         </is>
       </c>
       <c r="G308" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -24528,7 +24158,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N308" s="4" t="n"/>
+      <c r="N308" s="6" t="n">
+        <v>-7.68391249860852</v>
+      </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24536,14 +24168,10 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q308" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q308" s="4" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
@@ -24577,7 +24205,7 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
@@ -24609,7 +24237,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N309" s="4" t="n"/>
+      <c r="N309" s="6" t="n">
+        <v>23.3237302468182</v>
+      </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24617,14 +24247,10 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q309" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q309" s="4" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
@@ -24658,7 +24284,7 @@
         </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -24690,7 +24316,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N310" s="4" t="n"/>
+      <c r="N310" s="6" t="n">
+        <v>4.73750937705693</v>
+      </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24698,14 +24326,10 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q310" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q310" s="4" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
@@ -24739,7 +24363,7 @@
         </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -24771,7 +24395,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N311" s="4" t="n"/>
+      <c r="N311" s="6" t="n">
+        <v>-3.427271677593</v>
+      </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24779,14 +24405,10 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q311" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q311" s="4" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
@@ -24820,7 +24442,7 @@
         </is>
       </c>
       <c r="G312" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -24852,7 +24474,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N312" s="4" t="n"/>
+      <c r="N312" s="6" t="n">
+        <v>13.4067920775441</v>
+      </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24860,14 +24484,10 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q312" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q312" s="4" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
@@ -24901,7 +24521,7 @@
         </is>
       </c>
       <c r="G313" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
@@ -24933,7 +24553,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N313" s="4" t="n"/>
+      <c r="N313" s="6" t="n">
+        <v>2.81776735888189</v>
+      </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24941,14 +24563,10 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q313" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q313" s="4" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
@@ -24982,7 +24600,7 @@
         </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -25014,7 +24632,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N314" s="4" t="n"/>
+      <c r="N314" s="6" t="n">
+        <v>-7.21528827246595</v>
+      </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25022,14 +24642,10 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q314" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q314" s="4" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
@@ -25063,7 +24679,7 @@
         </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
@@ -25095,7 +24711,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N315" s="4" t="n"/>
+      <c r="N315" s="6" t="n">
+        <v>-11.5984250472679</v>
+      </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25103,14 +24721,10 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q315" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q315" s="4" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
@@ -25144,7 +24758,7 @@
         </is>
       </c>
       <c r="G316" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -25176,7 +24790,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N316" s="4" t="n"/>
+      <c r="N316" s="6" t="n">
+        <v>-9.9771448599891</v>
+      </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25184,14 +24800,10 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q316" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q316" s="4" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
@@ -25225,7 +24837,7 @@
         </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -25257,7 +24869,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N317" s="4" t="n"/>
+      <c r="N317" s="6" t="n">
+        <v>-2.04088217205993</v>
+      </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25265,14 +24879,10 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q317" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q317" s="4" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
@@ -25306,7 +24916,7 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
@@ -25338,7 +24948,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N318" s="4" t="n"/>
+      <c r="N318" s="6" t="n">
+        <v>1.48399647333513</v>
+      </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25346,14 +24958,10 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q318" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q318" s="4" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
@@ -25387,7 +24995,7 @@
         </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -25419,7 +25027,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N319" s="4" t="n"/>
+      <c r="N319" s="6" t="n">
+        <v>-6.01980277978769</v>
+      </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25427,14 +25037,10 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q319" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q319" s="4" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
@@ -25468,7 +25074,7 @@
         </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -25500,7 +25106,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N320" s="4" t="n"/>
+      <c r="N320" s="6" t="n">
+        <v>11.3296605279432</v>
+      </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25508,14 +25116,10 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q320" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q320" s="4" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
@@ -25549,7 +25153,7 @@
         </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
@@ -25581,7 +25185,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N321" s="4" t="n"/>
+      <c r="N321" s="6" t="n">
+        <v>-18.9896494698648</v>
+      </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25589,14 +25195,10 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q321" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q321" s="4" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
@@ -25630,7 +25232,7 @@
         </is>
       </c>
       <c r="G322" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
@@ -25662,7 +25264,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N322" s="4" t="n"/>
+      <c r="N322" s="6" t="n">
+        <v>-8.63099270105034</v>
+      </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25670,14 +25274,10 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q322" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q322" s="4" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
@@ -25711,7 +25311,7 @@
         </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -25743,7 +25343,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N323" s="4" t="n"/>
+      <c r="N323" s="6" t="n">
+        <v>-3.49269516009221</v>
+      </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25751,14 +25353,10 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q323" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q323" s="4" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
@@ -25792,7 +25390,7 @@
         </is>
       </c>
       <c r="G324" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
@@ -25824,7 +25422,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N324" s="4" t="n"/>
+      <c r="N324" s="6" t="n">
+        <v>-16.7579072328723</v>
+      </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25832,14 +25432,10 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q324" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q324" s="4" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
@@ -25873,7 +25469,7 @@
         </is>
       </c>
       <c r="G325" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
@@ -25905,7 +25501,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N325" s="4" t="n"/>
+      <c r="N325" s="6" t="n">
+        <v>-42.8355024477854</v>
+      </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25913,14 +25511,10 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q325" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
@@ -25954,7 +25548,7 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -25986,7 +25580,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N326" s="4" t="n"/>
+      <c r="N326" s="6" t="n">
+        <v>-49.1738717186218</v>
+      </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25994,14 +25590,10 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q326" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q326" s="4" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
@@ -26035,7 +25627,7 @@
         </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -26067,7 +25659,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N327" s="4" t="n"/>
+      <c r="N327" s="6" t="n">
+        <v>-70.4417611308894</v>
+      </c>
       <c r="O327" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26075,14 +25669,10 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q327" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q327" s="4" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
@@ -26116,7 +25706,7 @@
         </is>
       </c>
       <c r="G328" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -26148,7 +25738,9 @@
           <t>Tipo de interés real</t>
         </is>
       </c>
-      <c r="N328" s="4" t="n"/>
+      <c r="N328" s="6" t="n">
+        <v>-89.47199702962141</v>
+      </c>
       <c r="O328" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26156,14 +25748,10 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q328" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q328" s="4" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
@@ -26197,7 +25785,7 @@
         </is>
       </c>
       <c r="G329" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
@@ -26237,14 +25825,10 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q329" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q329" s="4" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
@@ -26278,7 +25862,7 @@
         </is>
       </c>
       <c r="G330" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -26318,14 +25902,10 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q330" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q330" s="4" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
@@ -26359,7 +25939,7 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -26399,14 +25979,10 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q331" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q331" s="4" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
@@ -26440,7 +26016,7 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
@@ -26480,14 +26056,10 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q332" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q332" s="4" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
@@ -26521,7 +26093,7 @@
         </is>
       </c>
       <c r="G333" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -26561,14 +26133,10 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q333" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q333" s="4" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
@@ -26602,7 +26170,7 @@
         </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -26642,14 +26210,10 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q334" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q334" s="4" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
@@ -26683,7 +26247,7 @@
         </is>
       </c>
       <c r="G335" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
@@ -26723,14 +26287,10 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q335" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q335" s="4" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
@@ -26764,7 +26324,7 @@
         </is>
       </c>
       <c r="G336" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
@@ -26804,14 +26364,10 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q336" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q336" s="4" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
@@ -26845,7 +26401,7 @@
         </is>
       </c>
       <c r="G337" s="5" t="n">
-        <v>2025</v>
+        <v>1960</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
         <is>
@@ -26859,22 +26415,22 @@
       </c>
       <c r="J337" s="4" t="inlineStr">
         <is>
-          <t>Sistema financiero</t>
+          <t>Deflactor</t>
         </is>
       </c>
       <c r="K337" s="4" t="inlineStr">
         <is>
-          <t>sistema_financiero</t>
+          <t>deflactor</t>
         </is>
       </c>
       <c r="L337" s="4" t="inlineStr">
         <is>
-          <t>FR.INR.RINR</t>
+          <t>NY.GDP.DEFL.KD.ZG</t>
         </is>
       </c>
       <c r="M337" s="4" t="inlineStr">
         <is>
-          <t>Tipo de interés real</t>
+          <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
       <c r="N337" s="4" t="n"/>
@@ -26885,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q337" s="4" t="inlineStr">
@@ -26926,7 +26482,7 @@
         </is>
       </c>
       <c r="G338" s="5" t="n">
-        <v>2026</v>
+        <v>1961</v>
       </c>
       <c r="H338" s="4" t="inlineStr">
         <is>
@@ -26940,22 +26496,22 @@
       </c>
       <c r="J338" s="4" t="inlineStr">
         <is>
-          <t>Sistema financiero</t>
+          <t>Deflactor</t>
         </is>
       </c>
       <c r="K338" s="4" t="inlineStr">
         <is>
-          <t>sistema_financiero</t>
+          <t>deflactor</t>
         </is>
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>FR.INR.RINR</t>
+          <t>NY.GDP.DEFL.KD.ZG</t>
         </is>
       </c>
       <c r="M338" s="4" t="inlineStr">
         <is>
-          <t>Tipo de interés real</t>
+          <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
       <c r="N338" s="4" t="n"/>
@@ -26966,7 +26522,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q338" s="4" t="inlineStr">
@@ -27007,7 +26563,7 @@
         </is>
       </c>
       <c r="G339" s="5" t="n">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="H339" s="4" t="inlineStr">
         <is>
@@ -27047,10 +26603,14 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q339" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q339" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
@@ -27084,7 +26644,7 @@
         </is>
       </c>
       <c r="G340" s="5" t="n">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="H340" s="4" t="inlineStr">
         <is>
@@ -27116,9 +26676,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N340" s="6" t="n">
-        <v>2.01373056168983</v>
-      </c>
+      <c r="N340" s="4" t="n"/>
       <c r="O340" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27126,10 +26684,14 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q340" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q340" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
@@ -27163,7 +26725,7 @@
         </is>
       </c>
       <c r="G341" s="5" t="n">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="H341" s="4" t="inlineStr">
         <is>
@@ -27195,9 +26757,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N341" s="6" t="n">
-        <v>0.6650541384622241</v>
-      </c>
+      <c r="N341" s="4" t="n"/>
       <c r="O341" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27205,10 +26765,14 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q341" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q341" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
@@ -27242,7 +26806,7 @@
         </is>
       </c>
       <c r="G342" s="5" t="n">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="H342" s="4" t="inlineStr">
         <is>
@@ -27274,9 +26838,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N342" s="6" t="n">
-        <v>4.91982977988773</v>
-      </c>
+      <c r="N342" s="4" t="n"/>
       <c r="O342" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27284,10 +26846,14 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q342" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q342" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
@@ -27321,7 +26887,7 @@
         </is>
       </c>
       <c r="G343" s="5" t="n">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="H343" s="4" t="inlineStr">
         <is>
@@ -27353,9 +26919,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N343" s="6" t="n">
-        <v>-0.366502858122402</v>
-      </c>
+      <c r="N343" s="4" t="n"/>
       <c r="O343" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27363,10 +26927,14 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q343" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q343" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
@@ -27400,7 +26968,7 @@
         </is>
       </c>
       <c r="G344" s="5" t="n">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="H344" s="4" t="inlineStr">
         <is>
@@ -27432,9 +27000,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N344" s="6" t="n">
-        <v>2.16720883620505</v>
-      </c>
+      <c r="N344" s="4" t="n"/>
       <c r="O344" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27442,10 +27008,14 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q344" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q344" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
@@ -27479,7 +27049,7 @@
         </is>
       </c>
       <c r="G345" s="5" t="n">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="H345" s="4" t="inlineStr">
         <is>
@@ -27511,9 +27081,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N345" s="6" t="n">
-        <v>2.64492682981677</v>
-      </c>
+      <c r="N345" s="4" t="n"/>
       <c r="O345" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27521,10 +27089,14 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q345" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q345" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
@@ -27558,7 +27130,7 @@
         </is>
       </c>
       <c r="G346" s="5" t="n">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="H346" s="4" t="inlineStr">
         <is>
@@ -27590,9 +27162,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N346" s="6" t="n">
-        <v>2.43422682068099</v>
-      </c>
+      <c r="N346" s="4" t="n"/>
       <c r="O346" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27600,10 +27170,14 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q346" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q346" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
@@ -27637,7 +27211,7 @@
         </is>
       </c>
       <c r="G347" s="5" t="n">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="H347" s="4" t="inlineStr">
         <is>
@@ -27669,9 +27243,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N347" s="6" t="n">
-        <v>1.06509902850236</v>
-      </c>
+      <c r="N347" s="4" t="n"/>
       <c r="O347" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27679,10 +27251,14 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q347" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q347" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
@@ -27716,7 +27292,7 @@
         </is>
       </c>
       <c r="G348" s="5" t="n">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="H348" s="4" t="inlineStr">
         <is>
@@ -27748,9 +27324,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N348" s="6" t="n">
-        <v>1.77946177900719</v>
-      </c>
+      <c r="N348" s="4" t="n"/>
       <c r="O348" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27758,10 +27332,14 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q348" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q348" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
@@ -27795,7 +27373,7 @@
         </is>
       </c>
       <c r="G349" s="5" t="n">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="H349" s="4" t="inlineStr">
         <is>
@@ -27827,9 +27405,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N349" s="6" t="n">
-        <v>4.35826317842816</v>
-      </c>
+      <c r="N349" s="4" t="n"/>
       <c r="O349" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27837,10 +27413,14 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q349" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q349" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
@@ -27874,7 +27454,7 @@
         </is>
       </c>
       <c r="G350" s="5" t="n">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="H350" s="4" t="inlineStr">
         <is>
@@ -27906,9 +27486,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N350" s="6" t="n">
-        <v>8.232657591742679</v>
-      </c>
+      <c r="N350" s="4" t="n"/>
       <c r="O350" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27916,10 +27494,14 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q350" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q350" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
@@ -27953,7 +27535,7 @@
         </is>
       </c>
       <c r="G351" s="5" t="n">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="H351" s="4" t="inlineStr">
         <is>
@@ -27985,9 +27567,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N351" s="6" t="n">
-        <v>6.26877681900034</v>
-      </c>
+      <c r="N351" s="4" t="n"/>
       <c r="O351" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27995,10 +27575,14 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q351" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q351" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
@@ -28032,7 +27616,7 @@
         </is>
       </c>
       <c r="G352" s="5" t="n">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="H352" s="4" t="inlineStr">
         <is>
@@ -28064,9 +27648,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N352" s="6" t="n">
-        <v>11.2003944899522</v>
-      </c>
+      <c r="N352" s="4" t="n"/>
       <c r="O352" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28074,10 +27656,14 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q352" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q352" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
@@ -28111,7 +27697,7 @@
         </is>
       </c>
       <c r="G353" s="5" t="n">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="H353" s="4" t="inlineStr">
         <is>
@@ -28143,9 +27729,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N353" s="6" t="n">
-        <v>50.107968794629</v>
-      </c>
+      <c r="N353" s="4" t="n"/>
       <c r="O353" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28153,10 +27737,14 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q353" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q353" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
@@ -28190,7 +27778,7 @@
         </is>
       </c>
       <c r="G354" s="5" t="n">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="H354" s="4" t="inlineStr">
         <is>
@@ -28222,9 +27810,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N354" s="6" t="n">
-        <v>2.26299814945894</v>
-      </c>
+      <c r="N354" s="4" t="n"/>
       <c r="O354" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28232,10 +27818,14 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q354" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q354" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
@@ -28269,7 +27859,7 @@
         </is>
       </c>
       <c r="G355" s="5" t="n">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="H355" s="4" t="inlineStr">
         <is>
@@ -28301,9 +27891,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N355" s="6" t="n">
-        <v>6.19354432405103</v>
-      </c>
+      <c r="N355" s="4" t="n"/>
       <c r="O355" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28311,10 +27899,14 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q355" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q355" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
@@ -28348,7 +27940,7 @@
         </is>
       </c>
       <c r="G356" s="5" t="n">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="H356" s="4" t="inlineStr">
         <is>
@@ -28380,9 +27972,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N356" s="6" t="n">
-        <v>8.44842727068664</v>
-      </c>
+      <c r="N356" s="4" t="n"/>
       <c r="O356" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28390,10 +27980,14 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q356" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q356" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
@@ -28427,7 +28021,7 @@
         </is>
       </c>
       <c r="G357" s="5" t="n">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="H357" s="4" t="inlineStr">
         <is>
@@ -28459,9 +28053,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N357" s="6" t="n">
-        <v>6.08667532833461</v>
-      </c>
+      <c r="N357" s="4" t="n"/>
       <c r="O357" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28469,10 +28061,14 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q357" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q357" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
@@ -28506,7 +28102,7 @@
         </is>
       </c>
       <c r="G358" s="5" t="n">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="H358" s="4" t="inlineStr">
         <is>
@@ -28538,9 +28134,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N358" s="6" t="n">
-        <v>21.9455792548796</v>
-      </c>
+      <c r="N358" s="4" t="n"/>
       <c r="O358" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28548,10 +28142,14 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q358" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q358" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
@@ -28585,7 +28183,7 @@
         </is>
       </c>
       <c r="G359" s="5" t="n">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="H359" s="4" t="inlineStr">
         <is>
@@ -28617,9 +28215,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N359" s="6" t="n">
-        <v>28.0272395381622</v>
-      </c>
+      <c r="N359" s="4" t="n"/>
       <c r="O359" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28627,10 +28223,14 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q359" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q359" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
@@ -28664,7 +28264,7 @@
         </is>
       </c>
       <c r="G360" s="5" t="n">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="H360" s="4" t="inlineStr">
         <is>
@@ -28696,9 +28296,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N360" s="6" t="n">
-        <v>13.6316657569901</v>
-      </c>
+      <c r="N360" s="4" t="n"/>
       <c r="O360" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28706,10 +28304,14 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q360" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q360" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
@@ -28743,7 +28345,7 @@
         </is>
       </c>
       <c r="G361" s="5" t="n">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="H361" s="4" t="inlineStr">
         <is>
@@ -28775,9 +28377,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N361" s="6" t="n">
-        <v>-0.42040040122437</v>
-      </c>
+      <c r="N361" s="4" t="n"/>
       <c r="O361" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28785,10 +28385,14 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q361" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q361" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
@@ -28822,7 +28426,7 @@
         </is>
       </c>
       <c r="G362" s="5" t="n">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="H362" s="4" t="inlineStr">
         <is>
@@ -28854,9 +28458,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N362" s="6" t="n">
-        <v>10.3947543511296</v>
-      </c>
+      <c r="N362" s="4" t="n"/>
       <c r="O362" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28864,10 +28466,14 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q362" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q362" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
@@ -28901,7 +28507,7 @@
         </is>
       </c>
       <c r="G363" s="5" t="n">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="H363" s="4" t="inlineStr">
         <is>
@@ -28933,9 +28539,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N363" s="6" t="n">
-        <v>37.4952567752211</v>
-      </c>
+      <c r="N363" s="4" t="n"/>
       <c r="O363" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28943,10 +28547,14 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q363" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q363" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
@@ -28980,7 +28588,7 @@
         </is>
       </c>
       <c r="G364" s="5" t="n">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="H364" s="4" t="inlineStr">
         <is>
@@ -29012,9 +28620,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N364" s="6" t="n">
-        <v>9.91291286624789</v>
-      </c>
+      <c r="N364" s="4" t="n"/>
       <c r="O364" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29022,10 +28628,14 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q364" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q364" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
@@ -29059,7 +28669,7 @@
         </is>
       </c>
       <c r="G365" s="5" t="n">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="H365" s="4" t="inlineStr">
         <is>
@@ -29091,9 +28701,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N365" s="6" t="n">
-        <v>-0.87769844706564</v>
-      </c>
+      <c r="N365" s="4" t="n"/>
       <c r="O365" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29101,10 +28709,14 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q365" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q365" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
@@ -29138,7 +28750,7 @@
         </is>
       </c>
       <c r="G366" s="5" t="n">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="H366" s="4" t="inlineStr">
         <is>
@@ -29170,9 +28782,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N366" s="6" t="n">
-        <v>35.7068476087747</v>
-      </c>
+      <c r="N366" s="4" t="n"/>
       <c r="O366" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29180,10 +28790,14 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q366" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q366" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
@@ -29217,7 +28831,7 @@
         </is>
       </c>
       <c r="G367" s="5" t="n">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="H367" s="4" t="inlineStr">
         <is>
@@ -29249,9 +28863,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N367" s="6" t="n">
-        <v>17.8169755565469</v>
-      </c>
+      <c r="N367" s="4" t="n"/>
       <c r="O367" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29259,10 +28871,14 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q367" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q367" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
@@ -29296,7 +28912,7 @@
         </is>
       </c>
       <c r="G368" s="5" t="n">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="H368" s="4" t="inlineStr">
         <is>
@@ -29328,9 +28944,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N368" s="6" t="n">
-        <v>101.132755331824</v>
-      </c>
+      <c r="N368" s="4" t="n"/>
       <c r="O368" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29338,10 +28952,14 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q368" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q368" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
@@ -29375,7 +28993,7 @@
         </is>
       </c>
       <c r="G369" s="5" t="n">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="H369" s="4" t="inlineStr">
         <is>
@@ -29407,9 +29025,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N369" s="6" t="n">
-        <v>41.4201088785186</v>
-      </c>
+      <c r="N369" s="4" t="n"/>
       <c r="O369" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29417,10 +29033,14 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q369" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q369" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
@@ -29454,7 +29074,7 @@
         </is>
       </c>
       <c r="G370" s="5" t="n">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="H370" s="4" t="inlineStr">
         <is>
@@ -29486,9 +29106,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N370" s="6" t="n">
-        <v>21.6148097546419</v>
-      </c>
+      <c r="N370" s="4" t="n"/>
       <c r="O370" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29496,10 +29114,14 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q370" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q370" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
@@ -29533,7 +29155,7 @@
         </is>
       </c>
       <c r="G371" s="5" t="n">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="H371" s="4" t="inlineStr">
         <is>
@@ -29565,9 +29187,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N371" s="6" t="n">
-        <v>28.3039973319823</v>
-      </c>
+      <c r="N371" s="4" t="n"/>
       <c r="O371" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29575,10 +29195,14 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q371" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q371" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
@@ -29612,7 +29236,7 @@
         </is>
       </c>
       <c r="G372" s="5" t="n">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="H372" s="4" t="inlineStr">
         <is>
@@ -29644,9 +29268,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N372" s="6" t="n">
-        <v>31.6690080487957</v>
-      </c>
+      <c r="N372" s="4" t="n"/>
       <c r="O372" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29654,10 +29276,14 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q372" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q372" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
@@ -29691,7 +29317,7 @@
         </is>
       </c>
       <c r="G373" s="5" t="n">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="H373" s="4" t="inlineStr">
         <is>
@@ -29723,9 +29349,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N373" s="6" t="n">
-        <v>62.8308497602543</v>
-      </c>
+      <c r="N373" s="4" t="n"/>
       <c r="O373" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29733,10 +29357,14 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q373" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q373" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
@@ -29770,7 +29398,7 @@
         </is>
       </c>
       <c r="G374" s="5" t="n">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="H374" s="4" t="inlineStr">
         <is>
@@ -29802,9 +29430,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N374" s="6" t="n">
-        <v>51.7661713803863</v>
-      </c>
+      <c r="N374" s="4" t="n"/>
       <c r="O374" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29812,10 +29438,14 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q374" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q374" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
@@ -29849,7 +29479,7 @@
         </is>
       </c>
       <c r="G375" s="5" t="n">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="H375" s="4" t="inlineStr">
         <is>
@@ -29881,9 +29511,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N375" s="6" t="n">
-        <v>115.644264591004</v>
-      </c>
+      <c r="N375" s="4" t="n"/>
       <c r="O375" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29891,10 +29519,14 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q375" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q375" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
@@ -29928,7 +29560,7 @@
         </is>
       </c>
       <c r="G376" s="5" t="n">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="H376" s="4" t="inlineStr">
         <is>
@@ -29960,9 +29592,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N376" s="6" t="n">
-        <v>33.9798981387027</v>
-      </c>
+      <c r="N376" s="4" t="n"/>
       <c r="O376" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29970,10 +29600,14 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q376" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q376" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
@@ -30007,7 +29641,7 @@
         </is>
       </c>
       <c r="G377" s="5" t="n">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="H377" s="4" t="inlineStr">
         <is>
@@ -30039,9 +29673,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N377" s="6" t="n">
-        <v>18.6734294422431</v>
-      </c>
+      <c r="N377" s="4" t="n"/>
       <c r="O377" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30049,10 +29681,14 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q377" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q377" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
@@ -30086,7 +29722,7 @@
         </is>
       </c>
       <c r="G378" s="5" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H378" s="4" t="inlineStr">
         <is>
@@ -30118,9 +29754,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N378" s="6" t="n">
-        <v>26.1494894419132</v>
-      </c>
+      <c r="N378" s="4" t="n"/>
       <c r="O378" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30128,10 +29762,14 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q378" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q378" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
@@ -30165,7 +29803,7 @@
         </is>
       </c>
       <c r="G379" s="5" t="n">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="H379" s="4" t="inlineStr">
         <is>
@@ -30197,9 +29835,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N379" s="6" t="n">
-        <v>29.6423626437172</v>
-      </c>
+      <c r="N379" s="4" t="n"/>
       <c r="O379" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30207,10 +29843,14 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q379" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q379" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
@@ -30244,7 +29884,7 @@
         </is>
       </c>
       <c r="G380" s="5" t="n">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="H380" s="4" t="inlineStr">
         <is>
@@ -30276,9 +29916,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N380" s="6" t="n">
-        <v>7.97560218698187</v>
-      </c>
+      <c r="N380" s="4" t="n"/>
       <c r="O380" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30286,10 +29924,14 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q380" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q380" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
@@ -30323,7 +29965,7 @@
         </is>
       </c>
       <c r="G381" s="5" t="n">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="H381" s="4" t="inlineStr">
         <is>
@@ -30355,9 +29997,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N381" s="6" t="n">
-        <v>32.8345319182831</v>
-      </c>
+      <c r="N381" s="4" t="n"/>
       <c r="O381" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30365,10 +30005,14 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q381" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q381" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
@@ -30402,7 +30046,7 @@
         </is>
       </c>
       <c r="G382" s="5" t="n">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="H382" s="4" t="inlineStr">
         <is>
@@ -30434,9 +30078,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N382" s="6" t="n">
-        <v>34.9288379544342</v>
-      </c>
+      <c r="N382" s="4" t="n"/>
       <c r="O382" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30444,10 +30086,14 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q382" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q382" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
@@ -30481,7 +30127,7 @@
         </is>
       </c>
       <c r="G383" s="5" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="H383" s="4" t="inlineStr">
         <is>
@@ -30513,9 +30159,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N383" s="6" t="n">
-        <v>34.0436148677513</v>
-      </c>
+      <c r="N383" s="4" t="n"/>
       <c r="O383" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30523,10 +30167,14 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q383" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q383" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
@@ -30560,7 +30208,7 @@
         </is>
       </c>
       <c r="G384" s="5" t="n">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="H384" s="4" t="inlineStr">
         <is>
@@ -30592,9 +30240,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N384" s="6" t="n">
-        <v>29.75501219662</v>
-      </c>
+      <c r="N384" s="4" t="n"/>
       <c r="O384" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30602,10 +30248,14 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q384" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q384" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
@@ -30639,7 +30289,7 @@
         </is>
       </c>
       <c r="G385" s="5" t="n">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="H385" s="4" t="inlineStr">
         <is>
@@ -30671,9 +30321,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N385" s="6" t="n">
-        <v>17.882509793009</v>
-      </c>
+      <c r="N385" s="4" t="n"/>
       <c r="O385" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30681,10 +30329,14 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q385" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q385" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
@@ -30718,7 +30370,7 @@
         </is>
       </c>
       <c r="G386" s="5" t="n">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="H386" s="4" t="inlineStr">
         <is>
@@ -30750,9 +30402,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N386" s="6" t="n">
-        <v>15.3925782088896</v>
-      </c>
+      <c r="N386" s="4" t="n"/>
       <c r="O386" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30760,10 +30410,14 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q386" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q386" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
@@ -30797,7 +30451,7 @@
         </is>
       </c>
       <c r="G387" s="5" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="H387" s="4" t="inlineStr">
         <is>
@@ -30829,9 +30483,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N387" s="6" t="n">
-        <v>30.2091684768406</v>
-      </c>
+      <c r="N387" s="4" t="n"/>
       <c r="O387" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30839,10 +30491,14 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q387" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q387" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
@@ -30876,7 +30532,7 @@
         </is>
       </c>
       <c r="G388" s="5" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="H388" s="4" t="inlineStr">
         <is>
@@ -30908,9 +30564,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N388" s="6" t="n">
-        <v>7.69217544074034</v>
-      </c>
+      <c r="N388" s="4" t="n"/>
       <c r="O388" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30918,10 +30572,14 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q388" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q388" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
@@ -30955,7 +30613,7 @@
         </is>
       </c>
       <c r="G389" s="5" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="H389" s="4" t="inlineStr">
         <is>
@@ -30987,9 +30645,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N389" s="6" t="n">
-        <v>46.0893567618569</v>
-      </c>
+      <c r="N389" s="4" t="n"/>
       <c r="O389" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30997,10 +30653,14 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q389" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q389" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
@@ -31034,7 +30694,7 @@
         </is>
       </c>
       <c r="G390" s="5" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H390" s="4" t="inlineStr">
         <is>
@@ -31066,9 +30726,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N390" s="6" t="n">
-        <v>28.2163432253321</v>
-      </c>
+      <c r="N390" s="4" t="n"/>
       <c r="O390" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31076,10 +30734,14 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q390" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q390" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
@@ -31113,7 +30775,7 @@
         </is>
       </c>
       <c r="G391" s="5" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H391" s="4" t="inlineStr">
         <is>
@@ -31145,9 +30807,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N391" s="6" t="n">
-        <v>20.5919077245585</v>
-      </c>
+      <c r="N391" s="4" t="n"/>
       <c r="O391" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31155,10 +30815,14 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q391" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q391" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
@@ -31192,7 +30856,7 @@
         </is>
       </c>
       <c r="G392" s="5" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="H392" s="4" t="inlineStr">
         <is>
@@ -31224,9 +30888,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N392" s="6" t="n">
-        <v>39.2264371875174</v>
-      </c>
+      <c r="N392" s="4" t="n"/>
       <c r="O392" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31234,10 +30896,14 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q392" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q392" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
@@ -31271,7 +30937,7 @@
         </is>
       </c>
       <c r="G393" s="5" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="H393" s="4" t="inlineStr">
         <is>
@@ -31303,9 +30969,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N393" s="6" t="n">
-        <v>105.042765502495</v>
-      </c>
+      <c r="N393" s="4" t="n"/>
       <c r="O393" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31313,10 +30977,14 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q393" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q393" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
@@ -31350,7 +31018,7 @@
         </is>
       </c>
       <c r="G394" s="5" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="H394" s="4" t="inlineStr">
         <is>
@@ -31382,9 +31050,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N394" s="6" t="n">
-        <v>134.908705496941</v>
-      </c>
+      <c r="N394" s="4" t="n"/>
       <c r="O394" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31392,10 +31058,14 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q394" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q394" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
@@ -31429,7 +31099,7 @@
         </is>
       </c>
       <c r="G395" s="5" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="H395" s="4" t="inlineStr">
         <is>
@@ -31461,9 +31131,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N395" s="6" t="n">
-        <v>308.600121728545</v>
-      </c>
+      <c r="N395" s="4" t="n"/>
       <c r="O395" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31471,10 +31139,14 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q395" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q395" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
@@ -31508,7 +31180,7 @@
         </is>
       </c>
       <c r="G396" s="5" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="H396" s="4" t="inlineStr">
         <is>
@@ -31540,9 +31212,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N396" s="6" t="n">
-        <v>1049.87777840941</v>
-      </c>
+      <c r="N396" s="4" t="n"/>
       <c r="O396" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31550,10 +31220,14 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q396" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q396" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
@@ -31587,7 +31261,7 @@
         </is>
       </c>
       <c r="G397" s="5" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="H397" s="4" t="inlineStr">
         <is>
@@ -31619,9 +31293,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N397" s="6" t="n">
-        <v>225652.234993614</v>
-      </c>
+      <c r="N397" s="4" t="n"/>
       <c r="O397" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31629,10 +31301,14 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q397" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q397" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
@@ -31666,7 +31342,7 @@
         </is>
       </c>
       <c r="G398" s="5" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="H398" s="4" t="inlineStr">
         <is>
@@ -31698,9 +31374,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N398" s="6" t="n">
-        <v>21909.3426680117</v>
-      </c>
+      <c r="N398" s="4" t="n"/>
       <c r="O398" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31708,10 +31382,14 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q398" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q398" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
@@ -31745,7 +31423,7 @@
         </is>
       </c>
       <c r="G399" s="5" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="H399" s="4" t="inlineStr">
         <is>
@@ -31777,9 +31455,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N399" s="6" t="n">
-        <v>1885.46577647144</v>
-      </c>
+      <c r="N399" s="4" t="n"/>
       <c r="O399" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31787,10 +31463,14 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q399" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q399" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
@@ -31824,7 +31504,7 @@
         </is>
       </c>
       <c r="G400" s="5" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="H400" s="4" t="inlineStr">
         <is>
@@ -31856,9 +31536,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N400" s="6" t="n">
-        <v>1212.84660038412</v>
-      </c>
+      <c r="N400" s="4" t="n"/>
       <c r="O400" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31866,10 +31544,14 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q400" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q400" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
@@ -31903,7 +31585,7 @@
         </is>
       </c>
       <c r="G401" s="5" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="H401" s="4" t="inlineStr">
         <is>
@@ -31935,9 +31617,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N401" s="6" t="n">
-        <v>210.806068385812</v>
-      </c>
+      <c r="N401" s="4" t="n"/>
       <c r="O401" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31945,10 +31625,14 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q401" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q401" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
@@ -31982,7 +31666,7 @@
         </is>
       </c>
       <c r="G402" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="H402" s="4" t="inlineStr">
         <is>
@@ -32014,9 +31698,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N402" s="6" t="n">
-        <v>367.798078256365</v>
-      </c>
+      <c r="N402" s="4" t="n"/>
       <c r="O402" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32024,10 +31706,14 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q402" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q402" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
@@ -32061,7 +31747,7 @@
         </is>
       </c>
       <c r="G403" s="5" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="H403" s="4" t="inlineStr">
         <is>
@@ -32093,9 +31779,7 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N403" s="6" t="n">
-        <v>55.4481074808972</v>
-      </c>
+      <c r="N403" s="4" t="n"/>
       <c r="O403" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32103,10 +31787,14 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q403" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q403" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="4" t="inlineStr">
@@ -32140,7 +31828,7 @@
         </is>
       </c>
       <c r="G404" s="5" t="n">
-        <v>2025</v>
+        <v>1960</v>
       </c>
       <c r="H404" s="4" t="inlineStr">
         <is>
@@ -32154,26 +31842,26 @@
       </c>
       <c r="J404" s="4" t="inlineStr">
         <is>
-          <t>Deflactor</t>
+          <t>Tipo de cambio</t>
         </is>
       </c>
       <c r="K404" s="4" t="inlineStr">
         <is>
-          <t>deflactor</t>
+          <t>tipo_de_cambio</t>
         </is>
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>NY.GDP.DEFL.KD.ZG</t>
+          <t>PA.NUS.FCRF</t>
         </is>
       </c>
       <c r="M404" s="4" t="inlineStr">
         <is>
-          <t>Inflación medida por el deflactor del PIB</t>
+          <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
       <c r="N404" s="6" t="n">
-        <v>227.093064600296</v>
+        <v>0.00334958333233334</v>
       </c>
       <c r="O404" s="4" t="inlineStr">
         <is>
@@ -32182,7 +31870,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32219,7 +31907,7 @@
         </is>
       </c>
       <c r="G405" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H405" s="4" t="inlineStr">
         <is>
@@ -32252,7 +31940,7 @@
         </is>
       </c>
       <c r="N405" s="6" t="n">
-        <v>0.00334958333233334</v>
+        <v>0.00334983333233333</v>
       </c>
       <c r="O405" s="4" t="inlineStr">
         <is>
@@ -32261,7 +31949,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32298,7 +31986,7 @@
         </is>
       </c>
       <c r="G406" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H406" s="4" t="inlineStr">
         <is>
@@ -32331,7 +32019,7 @@
         </is>
       </c>
       <c r="N406" s="6" t="n">
-        <v>0.00334983333233333</v>
+        <v>0.00334966666566667</v>
       </c>
       <c r="O406" s="4" t="inlineStr">
         <is>
@@ -32340,7 +32028,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32377,7 +32065,7 @@
         </is>
       </c>
       <c r="G407" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H407" s="4" t="inlineStr">
         <is>
@@ -32410,7 +32098,7 @@
         </is>
       </c>
       <c r="N407" s="6" t="n">
-        <v>0.00334966666566667</v>
+        <v>0.00334966666566666</v>
       </c>
       <c r="O407" s="4" t="inlineStr">
         <is>
@@ -32419,7 +32107,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32456,7 +32144,7 @@
         </is>
       </c>
       <c r="G408" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H408" s="4" t="inlineStr">
         <is>
@@ -32489,7 +32177,7 @@
         </is>
       </c>
       <c r="N408" s="6" t="n">
-        <v>0.00334966666566666</v>
+        <v>0.00435</v>
       </c>
       <c r="O408" s="4" t="inlineStr">
         <is>
@@ -32498,7 +32186,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32535,7 +32223,7 @@
         </is>
       </c>
       <c r="G409" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H409" s="4" t="inlineStr">
         <is>
@@ -32568,7 +32256,7 @@
         </is>
       </c>
       <c r="N409" s="6" t="n">
-        <v>0.00435</v>
+        <v>0.0044</v>
       </c>
       <c r="O409" s="4" t="inlineStr">
         <is>
@@ -32577,7 +32265,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32614,7 +32302,7 @@
         </is>
       </c>
       <c r="G410" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H410" s="4" t="inlineStr">
         <is>
@@ -32656,7 +32344,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32693,7 +32381,7 @@
         </is>
       </c>
       <c r="G411" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H411" s="4" t="inlineStr">
         <is>
@@ -32735,7 +32423,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32772,7 +32460,7 @@
         </is>
       </c>
       <c r="G412" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H412" s="4" t="inlineStr">
         <is>
@@ -32814,7 +32502,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32851,7 +32539,7 @@
         </is>
       </c>
       <c r="G413" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H413" s="4" t="inlineStr">
         <is>
@@ -32893,7 +32581,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32930,7 +32618,7 @@
         </is>
       </c>
       <c r="G414" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H414" s="4" t="inlineStr">
         <is>
@@ -32972,7 +32660,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -33009,7 +32697,7 @@
         </is>
       </c>
       <c r="G415" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H415" s="4" t="inlineStr">
         <is>
@@ -33051,7 +32739,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -33088,7 +32776,7 @@
         </is>
       </c>
       <c r="G416" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H416" s="4" t="inlineStr">
         <is>
@@ -33121,7 +32809,7 @@
         </is>
       </c>
       <c r="N416" s="6" t="n">
-        <v>0.0044</v>
+        <v>0.0043</v>
       </c>
       <c r="O416" s="4" t="inlineStr">
         <is>
@@ -33130,7 +32818,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -33167,7 +32855,7 @@
         </is>
       </c>
       <c r="G417" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H417" s="4" t="inlineStr">
         <is>
@@ -33209,7 +32897,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33246,7 +32934,7 @@
         </is>
       </c>
       <c r="G418" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H418" s="4" t="inlineStr">
         <is>
@@ -33288,7 +32976,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33325,7 +33013,7 @@
         </is>
       </c>
       <c r="G419" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H419" s="4" t="inlineStr">
         <is>
@@ -33367,7 +33055,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33404,7 +33092,7 @@
         </is>
       </c>
       <c r="G420" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H420" s="4" t="inlineStr">
         <is>
@@ -33446,7 +33134,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33483,7 +33171,7 @@
         </is>
       </c>
       <c r="G421" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H421" s="4" t="inlineStr">
         <is>
@@ -33525,7 +33213,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33562,7 +33250,7 @@
         </is>
       </c>
       <c r="G422" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H422" s="4" t="inlineStr">
         <is>
@@ -33604,7 +33292,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33641,7 +33329,7 @@
         </is>
       </c>
       <c r="G423" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H423" s="4" t="inlineStr">
         <is>
@@ -33683,7 +33371,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33720,7 +33408,7 @@
         </is>
       </c>
       <c r="G424" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H424" s="4" t="inlineStr">
         <is>
@@ -33762,7 +33450,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33799,7 +33487,7 @@
         </is>
       </c>
       <c r="G425" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H425" s="4" t="inlineStr">
         <is>
@@ -33841,7 +33529,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33878,7 +33566,7 @@
         </is>
       </c>
       <c r="G426" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H426" s="4" t="inlineStr">
         <is>
@@ -33920,7 +33608,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33957,7 +33645,7 @@
         </is>
       </c>
       <c r="G427" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H427" s="4" t="inlineStr">
         <is>
@@ -33999,7 +33687,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -34036,7 +33724,7 @@
         </is>
       </c>
       <c r="G428" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H428" s="4" t="inlineStr">
         <is>
@@ -34069,7 +33757,7 @@
         </is>
       </c>
       <c r="N428" s="6" t="n">
-        <v>0.0043</v>
+        <v>0.00701666666666667</v>
       </c>
       <c r="O428" s="4" t="inlineStr">
         <is>
@@ -34078,7 +33766,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -34115,7 +33803,7 @@
         </is>
       </c>
       <c r="G429" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H429" s="4" t="inlineStr">
         <is>
@@ -34148,7 +33836,7 @@
         </is>
       </c>
       <c r="N429" s="6" t="n">
-        <v>0.00701666666666667</v>
+        <v>0.0075</v>
       </c>
       <c r="O429" s="4" t="inlineStr">
         <is>
@@ -34157,7 +33845,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34194,7 +33882,7 @@
         </is>
       </c>
       <c r="G430" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H430" s="4" t="inlineStr">
         <is>
@@ -34227,7 +33915,7 @@
         </is>
       </c>
       <c r="N430" s="6" t="n">
-        <v>0.0075</v>
+        <v>0.00808333333333333</v>
       </c>
       <c r="O430" s="4" t="inlineStr">
         <is>
@@ -34236,7 +33924,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34273,7 +33961,7 @@
         </is>
       </c>
       <c r="G431" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H431" s="4" t="inlineStr">
         <is>
@@ -34306,7 +33994,7 @@
         </is>
       </c>
       <c r="N431" s="6" t="n">
-        <v>0.00808333333333333</v>
+        <v>0.0145</v>
       </c>
       <c r="O431" s="4" t="inlineStr">
         <is>
@@ -34315,7 +34003,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34352,7 +34040,7 @@
         </is>
       </c>
       <c r="G432" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H432" s="4" t="inlineStr">
         <is>
@@ -34394,7 +34082,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34431,7 +34119,7 @@
         </is>
       </c>
       <c r="G433" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H433" s="4" t="inlineStr">
         <is>
@@ -34464,7 +34152,7 @@
         </is>
       </c>
       <c r="N433" s="6" t="n">
-        <v>0.0145</v>
+        <v>0.0346916666666667</v>
       </c>
       <c r="O433" s="4" t="inlineStr">
         <is>
@@ -34473,7 +34161,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34510,7 +34198,7 @@
         </is>
       </c>
       <c r="G434" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H434" s="4" t="inlineStr">
         <is>
@@ -34543,7 +34231,7 @@
         </is>
       </c>
       <c r="N434" s="6" t="n">
-        <v>0.0346916666666667</v>
+        <v>0.0468916666666667</v>
       </c>
       <c r="O434" s="4" t="inlineStr">
         <is>
@@ -34552,7 +34240,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34589,7 +34277,7 @@
         </is>
       </c>
       <c r="G435" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H435" s="4" t="inlineStr">
         <is>
@@ -34622,7 +34310,7 @@
         </is>
       </c>
       <c r="N435" s="6" t="n">
-        <v>0.0468916666666667</v>
+        <v>0.056825</v>
       </c>
       <c r="O435" s="4" t="inlineStr">
         <is>
@@ -34631,7 +34319,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34668,7 +34356,7 @@
         </is>
       </c>
       <c r="G436" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H436" s="4" t="inlineStr">
         <is>
@@ -34701,7 +34389,7 @@
         </is>
       </c>
       <c r="N436" s="6" t="n">
-        <v>0.056825</v>
+        <v>0.0683833333333333</v>
       </c>
       <c r="O436" s="4" t="inlineStr">
         <is>
@@ -34710,7 +34398,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34747,7 +34435,7 @@
         </is>
       </c>
       <c r="G437" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H437" s="4" t="inlineStr">
         <is>
@@ -34780,7 +34468,7 @@
         </is>
       </c>
       <c r="N437" s="6" t="n">
-        <v>0.0683833333333333</v>
+        <v>0.0908416666666667</v>
       </c>
       <c r="O437" s="4" t="inlineStr">
         <is>
@@ -34789,7 +34477,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34826,7 +34514,7 @@
         </is>
       </c>
       <c r="G438" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H438" s="4" t="inlineStr">
         <is>
@@ -34859,7 +34547,7 @@
         </is>
       </c>
       <c r="N438" s="6" t="n">
-        <v>0.0908416666666667</v>
+        <v>0.146858333333333</v>
       </c>
       <c r="O438" s="4" t="inlineStr">
         <is>
@@ -34868,7 +34556,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34905,7 +34593,7 @@
         </is>
       </c>
       <c r="G439" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H439" s="4" t="inlineStr">
         <is>
@@ -34938,7 +34626,7 @@
         </is>
       </c>
       <c r="N439" s="6" t="n">
-        <v>0.146858333333333</v>
+        <v>0.176841666666667</v>
       </c>
       <c r="O439" s="4" t="inlineStr">
         <is>
@@ -34947,7 +34635,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34984,7 +34672,7 @@
         </is>
       </c>
       <c r="G440" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H440" s="4" t="inlineStr">
         <is>
@@ -35017,7 +34705,7 @@
         </is>
       </c>
       <c r="N440" s="6" t="n">
-        <v>0.176841666666667</v>
+        <v>0.41735</v>
       </c>
       <c r="O440" s="4" t="inlineStr">
         <is>
@@ -35026,7 +34714,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -35063,7 +34751,7 @@
         </is>
       </c>
       <c r="G441" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H441" s="4" t="inlineStr">
         <is>
@@ -35096,7 +34784,7 @@
         </is>
       </c>
       <c r="N441" s="6" t="n">
-        <v>0.41735</v>
+        <v>0.488633333333333</v>
       </c>
       <c r="O441" s="4" t="inlineStr">
         <is>
@@ -35105,7 +34793,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -35142,7 +34830,7 @@
         </is>
       </c>
       <c r="G442" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H442" s="4" t="inlineStr">
         <is>
@@ -35175,7 +34863,7 @@
         </is>
       </c>
       <c r="N442" s="6" t="n">
-        <v>0.488633333333333</v>
+        <v>0.547566666666667</v>
       </c>
       <c r="O442" s="4" t="inlineStr">
         <is>
@@ -35184,7 +34872,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35221,7 +34909,7 @@
         </is>
       </c>
       <c r="G443" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H443" s="4" t="inlineStr">
         <is>
@@ -35254,7 +34942,7 @@
         </is>
       </c>
       <c r="N443" s="6" t="n">
-        <v>0.547566666666667</v>
+        <v>0.605725</v>
       </c>
       <c r="O443" s="4" t="inlineStr">
         <is>
@@ -35263,7 +34951,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35300,7 +34988,7 @@
         </is>
       </c>
       <c r="G444" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H444" s="4" t="inlineStr">
         <is>
@@ -35333,7 +35021,7 @@
         </is>
       </c>
       <c r="N444" s="6" t="n">
-        <v>0.605725</v>
+        <v>0.6799666666666671</v>
       </c>
       <c r="O444" s="4" t="inlineStr">
         <is>
@@ -35342,7 +35030,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35379,7 +35067,7 @@
         </is>
       </c>
       <c r="G445" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H445" s="4" t="inlineStr">
         <is>
@@ -35412,7 +35100,7 @@
         </is>
       </c>
       <c r="N445" s="6" t="n">
-        <v>0.6799666666666671</v>
+        <v>0.723658333333334</v>
       </c>
       <c r="O445" s="4" t="inlineStr">
         <is>
@@ -35421,7 +35109,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35458,7 +35146,7 @@
         </is>
       </c>
       <c r="G446" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H446" s="4" t="inlineStr">
         <is>
@@ -35491,7 +35179,7 @@
         </is>
       </c>
       <c r="N446" s="6" t="n">
-        <v>0.723658333333334</v>
+        <v>1.16095</v>
       </c>
       <c r="O446" s="4" t="inlineStr">
         <is>
@@ -35500,7 +35188,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35537,7 +35225,7 @@
         </is>
       </c>
       <c r="G447" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H447" s="4" t="inlineStr">
         <is>
@@ -35570,7 +35258,7 @@
         </is>
       </c>
       <c r="N447" s="6" t="n">
-        <v>1.16095</v>
+        <v>1.60695833333333</v>
       </c>
       <c r="O447" s="4" t="inlineStr">
         <is>
@@ -35579,7 +35267,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35616,7 +35304,7 @@
         </is>
       </c>
       <c r="G448" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H448" s="4" t="inlineStr">
         <is>
@@ -35649,7 +35337,7 @@
         </is>
       </c>
       <c r="N448" s="6" t="n">
-        <v>1.60695833333333</v>
+        <v>1.89133333333333</v>
       </c>
       <c r="O448" s="4" t="inlineStr">
         <is>
@@ -35658,7 +35346,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35695,7 +35383,7 @@
         </is>
       </c>
       <c r="G449" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H449" s="4" t="inlineStr">
         <is>
@@ -35728,7 +35416,7 @@
         </is>
       </c>
       <c r="N449" s="6" t="n">
-        <v>1.89133333333333</v>
+        <v>2.08975</v>
       </c>
       <c r="O449" s="4" t="inlineStr">
         <is>
@@ -35737,7 +35425,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35774,7 +35462,7 @@
         </is>
       </c>
       <c r="G450" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H450" s="4" t="inlineStr">
         <is>
@@ -35807,7 +35495,7 @@
         </is>
       </c>
       <c r="N450" s="6" t="n">
-        <v>2.08975</v>
+        <v>2.147</v>
       </c>
       <c r="O450" s="4" t="inlineStr">
         <is>
@@ -35816,7 +35504,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35853,7 +35541,7 @@
         </is>
       </c>
       <c r="G451" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H451" s="4" t="inlineStr">
         <is>
@@ -35895,7 +35583,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35932,7 +35620,7 @@
         </is>
       </c>
       <c r="G452" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H452" s="4" t="inlineStr">
         <is>
@@ -35974,7 +35662,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -36011,7 +35699,7 @@
         </is>
       </c>
       <c r="G453" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H453" s="4" t="inlineStr">
         <is>
@@ -36053,7 +35741,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -36090,7 +35778,7 @@
         </is>
       </c>
       <c r="G454" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H454" s="4" t="inlineStr">
         <is>
@@ -36123,7 +35811,7 @@
         </is>
       </c>
       <c r="N454" s="6" t="n">
-        <v>2.147</v>
+        <v>2.58206031746032</v>
       </c>
       <c r="O454" s="4" t="inlineStr">
         <is>
@@ -36132,7 +35820,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -36169,7 +35857,7 @@
         </is>
       </c>
       <c r="G455" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H455" s="4" t="inlineStr">
         <is>
@@ -36202,7 +35890,7 @@
         </is>
       </c>
       <c r="N455" s="6" t="n">
-        <v>2.58206031746032</v>
+        <v>4.2893</v>
       </c>
       <c r="O455" s="4" t="inlineStr">
         <is>
@@ -36211,7 +35899,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36248,7 +35936,7 @@
         </is>
       </c>
       <c r="G456" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H456" s="4" t="inlineStr">
         <is>
@@ -36290,7 +35978,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36327,7 +36015,7 @@
         </is>
       </c>
       <c r="G457" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H457" s="4" t="inlineStr">
         <is>
@@ -36360,7 +36048,7 @@
         </is>
       </c>
       <c r="N457" s="6" t="n">
-        <v>4.2893</v>
+        <v>6.04796184166667</v>
       </c>
       <c r="O457" s="4" t="inlineStr">
         <is>
@@ -36369,7 +36057,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36406,7 +36094,7 @@
         </is>
       </c>
       <c r="G458" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H458" s="4" t="inlineStr">
         <is>
@@ -36439,7 +36127,7 @@
         </is>
       </c>
       <c r="N458" s="6" t="n">
-        <v>6.04796184166667</v>
+        <v>6.2842</v>
       </c>
       <c r="O458" s="4" t="inlineStr">
         <is>
@@ -36448,7 +36136,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36485,7 +36173,7 @@
         </is>
       </c>
       <c r="G459" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H459" s="4" t="inlineStr">
         <is>
@@ -36527,7 +36215,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36564,7 +36252,7 @@
         </is>
       </c>
       <c r="G460" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H460" s="4" t="inlineStr">
         <is>
@@ -36597,7 +36285,7 @@
         </is>
       </c>
       <c r="N460" s="6" t="n">
-        <v>6.2842</v>
+        <v>9.257344444441671</v>
       </c>
       <c r="O460" s="4" t="inlineStr">
         <is>
@@ -36606,7 +36294,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36643,7 +36331,7 @@
         </is>
       </c>
       <c r="G461" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H461" s="4" t="inlineStr">
         <is>
@@ -36676,7 +36364,7 @@
         </is>
       </c>
       <c r="N461" s="6" t="n">
-        <v>9.257344444441671</v>
+        <v>9.975</v>
       </c>
       <c r="O461" s="4" t="inlineStr">
         <is>
@@ -36685,7 +36373,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36722,7 +36410,7 @@
         </is>
       </c>
       <c r="G462" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H462" s="4" t="inlineStr">
         <is>
@@ -36754,9 +36442,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N462" s="6" t="n">
-        <v>9.975</v>
-      </c>
+      <c r="N462" s="4" t="n"/>
       <c r="O462" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36764,7 +36450,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36801,7 +36487,7 @@
         </is>
       </c>
       <c r="G463" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H463" s="4" t="inlineStr">
         <is>
@@ -36841,7 +36527,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36878,7 +36564,7 @@
         </is>
       </c>
       <c r="G464" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H464" s="4" t="inlineStr">
         <is>
@@ -36918,7 +36604,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36955,7 +36641,7 @@
         </is>
       </c>
       <c r="G465" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H465" s="4" t="inlineStr">
         <is>
@@ -36995,7 +36681,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -37032,7 +36718,7 @@
         </is>
       </c>
       <c r="G466" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H466" s="4" t="inlineStr">
         <is>
@@ -37072,7 +36758,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -37109,7 +36795,7 @@
         </is>
       </c>
       <c r="G467" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H467" s="4" t="inlineStr">
         <is>
@@ -37149,7 +36835,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37186,7 +36872,7 @@
         </is>
       </c>
       <c r="G468" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H468" s="4" t="inlineStr">
         <is>
@@ -37226,7 +36912,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37263,7 +36949,7 @@
         </is>
       </c>
       <c r="G469" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H469" s="4" t="inlineStr">
         <is>
@@ -37303,87 +36989,10 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
-    </row>
-    <row r="470">
-      <c r="A470" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B470" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C470" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D470" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E470" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F470" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G470" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H470" s="4" t="inlineStr">
-        <is>
-          <t>Precios e inflación</t>
-        </is>
-      </c>
-      <c r="I470" s="4" t="inlineStr">
-        <is>
-          <t>precios_e_inflacion</t>
-        </is>
-      </c>
-      <c r="J470" s="4" t="inlineStr">
-        <is>
-          <t>Tipo de cambio</t>
-        </is>
-      </c>
-      <c r="K470" s="4" t="inlineStr">
-        <is>
-          <t>tipo_de_cambio</t>
-        </is>
-      </c>
-      <c r="L470" s="4" t="inlineStr">
-        <is>
-          <t>PA.NUS.FCRF</t>
-        </is>
-      </c>
-      <c r="M470" s="4" t="inlineStr">
-        <is>
-          <t>Tipo de cambio oficial moneda local por dólar</t>
-        </is>
-      </c>
-      <c r="N470" s="4" t="n"/>
-      <c r="O470" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P470" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q470" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -37465,7 +37074,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -37486,7 +37095,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q469"/>
+  <dimension ref="A1:Q468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18118,7 +18118,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18272,7 +18272,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18580,7 +18580,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19042,7 +19042,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20047,7 +20047,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20598,7 +20598,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20983,7 +20983,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21214,7 +21214,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21291,7 +21291,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21445,7 +21445,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22523,7 +22523,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22600,7 +22600,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22677,7 +22677,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22754,7 +22754,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23141,7 +23141,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23220,7 +23220,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23378,7 +23378,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23615,7 +23615,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24010,7 +24010,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24089,7 +24089,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24168,7 +24168,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24405,7 +24405,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24484,7 +24484,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24721,7 +24721,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24958,7 +24958,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25037,7 +25037,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25432,7 +25432,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25511,7 +25511,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25748,7 +25748,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25902,7 +25902,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26056,7 +26056,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26210,7 +26210,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26287,7 +26287,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,14 +26441,10 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q337" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q337" s="4" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
@@ -26514,7 +26510,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N338" s="4" t="n"/>
+      <c r="N338" s="6" t="n">
+        <v>2.01373056168983</v>
+      </c>
       <c r="O338" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26522,14 +26520,10 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q338" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q338" s="4" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
@@ -26595,7 +26589,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N339" s="4" t="n"/>
+      <c r="N339" s="6" t="n">
+        <v>0.6650541384622241</v>
+      </c>
       <c r="O339" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26603,14 +26599,10 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q339" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q339" s="4" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
@@ -26676,7 +26668,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N340" s="4" t="n"/>
+      <c r="N340" s="6" t="n">
+        <v>4.91982977988773</v>
+      </c>
       <c r="O340" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26684,14 +26678,10 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q340" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q340" s="4" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
@@ -26757,7 +26747,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N341" s="4" t="n"/>
+      <c r="N341" s="6" t="n">
+        <v>-0.366502858122402</v>
+      </c>
       <c r="O341" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26765,14 +26757,10 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q341" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q341" s="4" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
@@ -26838,7 +26826,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N342" s="4" t="n"/>
+      <c r="N342" s="6" t="n">
+        <v>2.16720883620505</v>
+      </c>
       <c r="O342" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26846,14 +26836,10 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q342" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q342" s="4" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
@@ -26919,7 +26905,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N343" s="4" t="n"/>
+      <c r="N343" s="6" t="n">
+        <v>2.64492682981677</v>
+      </c>
       <c r="O343" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26927,14 +26915,10 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q343" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q343" s="4" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
@@ -27000,7 +26984,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N344" s="4" t="n"/>
+      <c r="N344" s="6" t="n">
+        <v>2.43422682068099</v>
+      </c>
       <c r="O344" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27008,14 +26994,10 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q344" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q344" s="4" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
@@ -27081,7 +27063,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N345" s="4" t="n"/>
+      <c r="N345" s="6" t="n">
+        <v>1.06509902850236</v>
+      </c>
       <c r="O345" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27089,14 +27073,10 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q345" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q345" s="4" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
@@ -27162,7 +27142,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N346" s="4" t="n"/>
+      <c r="N346" s="6" t="n">
+        <v>1.77946177900719</v>
+      </c>
       <c r="O346" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27170,14 +27152,10 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q346" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q346" s="4" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
@@ -27243,7 +27221,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N347" s="4" t="n"/>
+      <c r="N347" s="6" t="n">
+        <v>4.35826317842816</v>
+      </c>
       <c r="O347" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27251,14 +27231,10 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q347" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q347" s="4" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
@@ -27324,7 +27300,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N348" s="4" t="n"/>
+      <c r="N348" s="6" t="n">
+        <v>8.232657591742679</v>
+      </c>
       <c r="O348" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27332,14 +27310,10 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q348" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q348" s="4" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
@@ -27405,7 +27379,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N349" s="4" t="n"/>
+      <c r="N349" s="6" t="n">
+        <v>6.26877681900034</v>
+      </c>
       <c r="O349" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27413,14 +27389,10 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q349" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q349" s="4" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
@@ -27486,7 +27458,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N350" s="4" t="n"/>
+      <c r="N350" s="6" t="n">
+        <v>11.2003944899522</v>
+      </c>
       <c r="O350" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27494,14 +27468,10 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q350" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q350" s="4" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
@@ -27567,7 +27537,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N351" s="4" t="n"/>
+      <c r="N351" s="6" t="n">
+        <v>50.107968794629</v>
+      </c>
       <c r="O351" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27575,14 +27547,10 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q351" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q351" s="4" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
@@ -27648,7 +27616,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N352" s="4" t="n"/>
+      <c r="N352" s="6" t="n">
+        <v>2.26299814945894</v>
+      </c>
       <c r="O352" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27656,14 +27626,10 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q352" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q352" s="4" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
@@ -27729,7 +27695,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N353" s="4" t="n"/>
+      <c r="N353" s="6" t="n">
+        <v>6.19354432405103</v>
+      </c>
       <c r="O353" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27737,14 +27705,10 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q353" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q353" s="4" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
@@ -27810,7 +27774,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N354" s="4" t="n"/>
+      <c r="N354" s="6" t="n">
+        <v>8.44842727068664</v>
+      </c>
       <c r="O354" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27818,14 +27784,10 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q354" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q354" s="4" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
@@ -27891,7 +27853,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N355" s="4" t="n"/>
+      <c r="N355" s="6" t="n">
+        <v>6.08667532833461</v>
+      </c>
       <c r="O355" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27899,14 +27863,10 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q355" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q355" s="4" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
@@ -27972,7 +27932,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N356" s="4" t="n"/>
+      <c r="N356" s="6" t="n">
+        <v>21.9455792548796</v>
+      </c>
       <c r="O356" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -27980,14 +27942,10 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q356" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q356" s="4" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
@@ -28053,7 +28011,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N357" s="4" t="n"/>
+      <c r="N357" s="6" t="n">
+        <v>28.0272395381622</v>
+      </c>
       <c r="O357" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28061,14 +28021,10 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q357" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q357" s="4" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
@@ -28134,7 +28090,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N358" s="4" t="n"/>
+      <c r="N358" s="6" t="n">
+        <v>13.6316657569901</v>
+      </c>
       <c r="O358" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28142,14 +28100,10 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q358" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q358" s="4" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
@@ -28215,7 +28169,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N359" s="4" t="n"/>
+      <c r="N359" s="6" t="n">
+        <v>-0.42040040122437</v>
+      </c>
       <c r="O359" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28223,14 +28179,10 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q359" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q359" s="4" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
@@ -28296,7 +28248,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N360" s="4" t="n"/>
+      <c r="N360" s="6" t="n">
+        <v>10.3947543511296</v>
+      </c>
       <c r="O360" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28304,14 +28258,10 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q360" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q360" s="4" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
@@ -28377,7 +28327,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N361" s="4" t="n"/>
+      <c r="N361" s="6" t="n">
+        <v>37.4952567752211</v>
+      </c>
       <c r="O361" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28385,14 +28337,10 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q361" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q361" s="4" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
@@ -28458,7 +28406,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N362" s="4" t="n"/>
+      <c r="N362" s="6" t="n">
+        <v>9.91291286624789</v>
+      </c>
       <c r="O362" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28466,14 +28416,10 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q362" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q362" s="4" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
@@ -28539,7 +28485,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N363" s="4" t="n"/>
+      <c r="N363" s="6" t="n">
+        <v>-0.87769844706564</v>
+      </c>
       <c r="O363" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28547,14 +28495,10 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q363" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q363" s="4" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
@@ -28620,7 +28564,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N364" s="4" t="n"/>
+      <c r="N364" s="6" t="n">
+        <v>35.7068476087747</v>
+      </c>
       <c r="O364" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28628,14 +28574,10 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q364" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q364" s="4" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
@@ -28701,7 +28643,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N365" s="4" t="n"/>
+      <c r="N365" s="6" t="n">
+        <v>17.8169755565469</v>
+      </c>
       <c r="O365" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28709,14 +28653,10 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q365" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q365" s="4" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
@@ -28782,7 +28722,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N366" s="4" t="n"/>
+      <c r="N366" s="6" t="n">
+        <v>101.132755331824</v>
+      </c>
       <c r="O366" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28790,14 +28732,10 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q366" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q366" s="4" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
@@ -28863,7 +28801,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N367" s="4" t="n"/>
+      <c r="N367" s="6" t="n">
+        <v>41.4201088785186</v>
+      </c>
       <c r="O367" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28871,14 +28811,10 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q367" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q367" s="4" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
@@ -28944,7 +28880,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N368" s="4" t="n"/>
+      <c r="N368" s="6" t="n">
+        <v>21.6148097546419</v>
+      </c>
       <c r="O368" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -28952,14 +28890,10 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q368" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q368" s="4" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
@@ -29025,7 +28959,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N369" s="4" t="n"/>
+      <c r="N369" s="6" t="n">
+        <v>28.3039973319823</v>
+      </c>
       <c r="O369" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29033,14 +28969,10 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q369" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q369" s="4" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
@@ -29106,7 +29038,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N370" s="4" t="n"/>
+      <c r="N370" s="6" t="n">
+        <v>31.6690080487957</v>
+      </c>
       <c r="O370" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29114,14 +29048,10 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q370" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q370" s="4" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
@@ -29187,7 +29117,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N371" s="4" t="n"/>
+      <c r="N371" s="6" t="n">
+        <v>62.8308497602543</v>
+      </c>
       <c r="O371" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29195,14 +29127,10 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q371" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q371" s="4" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
@@ -29268,7 +29196,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N372" s="4" t="n"/>
+      <c r="N372" s="6" t="n">
+        <v>51.7661713803863</v>
+      </c>
       <c r="O372" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29276,14 +29206,10 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q372" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q372" s="4" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
@@ -29349,7 +29275,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N373" s="4" t="n"/>
+      <c r="N373" s="6" t="n">
+        <v>115.644264591004</v>
+      </c>
       <c r="O373" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29357,14 +29285,10 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q373" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q373" s="4" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
@@ -29430,7 +29354,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N374" s="4" t="n"/>
+      <c r="N374" s="6" t="n">
+        <v>33.9798981387027</v>
+      </c>
       <c r="O374" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29438,14 +29364,10 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q374" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q374" s="4" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
@@ -29511,7 +29433,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N375" s="4" t="n"/>
+      <c r="N375" s="6" t="n">
+        <v>18.6734294422431</v>
+      </c>
       <c r="O375" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29519,14 +29443,10 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q375" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q375" s="4" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
@@ -29592,7 +29512,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N376" s="4" t="n"/>
+      <c r="N376" s="6" t="n">
+        <v>26.1494894419132</v>
+      </c>
       <c r="O376" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29600,14 +29522,10 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q376" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q376" s="4" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
@@ -29673,7 +29591,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N377" s="4" t="n"/>
+      <c r="N377" s="6" t="n">
+        <v>29.6423626437172</v>
+      </c>
       <c r="O377" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29681,14 +29601,10 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q377" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q377" s="4" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
@@ -29754,7 +29670,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N378" s="4" t="n"/>
+      <c r="N378" s="6" t="n">
+        <v>7.97560218698187</v>
+      </c>
       <c r="O378" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29762,14 +29680,10 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q378" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q378" s="4" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
@@ -29835,7 +29749,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N379" s="4" t="n"/>
+      <c r="N379" s="6" t="n">
+        <v>32.8345319182831</v>
+      </c>
       <c r="O379" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29843,14 +29759,10 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q379" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q379" s="4" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
@@ -29916,7 +29828,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N380" s="4" t="n"/>
+      <c r="N380" s="6" t="n">
+        <v>34.9288379544342</v>
+      </c>
       <c r="O380" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -29924,14 +29838,10 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q380" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q380" s="4" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
@@ -29997,7 +29907,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N381" s="4" t="n"/>
+      <c r="N381" s="6" t="n">
+        <v>34.0436148677513</v>
+      </c>
       <c r="O381" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30005,14 +29917,10 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q381" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q381" s="4" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
@@ -30078,7 +29986,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N382" s="4" t="n"/>
+      <c r="N382" s="6" t="n">
+        <v>29.75501219662</v>
+      </c>
       <c r="O382" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30086,14 +29996,10 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q382" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q382" s="4" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
@@ -30159,7 +30065,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N383" s="4" t="n"/>
+      <c r="N383" s="6" t="n">
+        <v>17.882509793009</v>
+      </c>
       <c r="O383" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30167,14 +30075,10 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q383" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q383" s="4" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
@@ -30240,7 +30144,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N384" s="4" t="n"/>
+      <c r="N384" s="6" t="n">
+        <v>15.3925782088896</v>
+      </c>
       <c r="O384" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30248,14 +30154,10 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q384" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q384" s="4" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
@@ -30321,7 +30223,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N385" s="4" t="n"/>
+      <c r="N385" s="6" t="n">
+        <v>30.2091684768406</v>
+      </c>
       <c r="O385" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30329,14 +30233,10 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q385" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q385" s="4" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
@@ -30402,7 +30302,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N386" s="4" t="n"/>
+      <c r="N386" s="6" t="n">
+        <v>7.69217544074034</v>
+      </c>
       <c r="O386" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30410,14 +30312,10 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q386" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q386" s="4" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
@@ -30483,7 +30381,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N387" s="4" t="n"/>
+      <c r="N387" s="6" t="n">
+        <v>46.0893567618569</v>
+      </c>
       <c r="O387" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30491,14 +30391,10 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q387" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q387" s="4" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
@@ -30564,7 +30460,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N388" s="4" t="n"/>
+      <c r="N388" s="6" t="n">
+        <v>28.2163432253321</v>
+      </c>
       <c r="O388" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30572,14 +30470,10 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q388" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q388" s="4" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
@@ -30645,7 +30539,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N389" s="4" t="n"/>
+      <c r="N389" s="6" t="n">
+        <v>20.5919077245585</v>
+      </c>
       <c r="O389" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30653,14 +30549,10 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q389" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q389" s="4" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
@@ -30726,7 +30618,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N390" s="4" t="n"/>
+      <c r="N390" s="6" t="n">
+        <v>39.2264371875174</v>
+      </c>
       <c r="O390" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30734,14 +30628,10 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q390" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q390" s="4" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
@@ -30807,7 +30697,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N391" s="4" t="n"/>
+      <c r="N391" s="6" t="n">
+        <v>105.042765502495</v>
+      </c>
       <c r="O391" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30815,14 +30707,10 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q391" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q391" s="4" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
@@ -30888,7 +30776,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N392" s="4" t="n"/>
+      <c r="N392" s="6" t="n">
+        <v>134.908705496941</v>
+      </c>
       <c r="O392" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30896,14 +30786,10 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q392" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q392" s="4" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
@@ -30969,7 +30855,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N393" s="4" t="n"/>
+      <c r="N393" s="6" t="n">
+        <v>308.600121728545</v>
+      </c>
       <c r="O393" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -30977,14 +30865,10 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q393" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q393" s="4" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
@@ -31050,7 +30934,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N394" s="4" t="n"/>
+      <c r="N394" s="6" t="n">
+        <v>1049.87777840941</v>
+      </c>
       <c r="O394" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31058,14 +30944,10 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q394" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q394" s="4" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
@@ -31131,7 +31013,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N395" s="4" t="n"/>
+      <c r="N395" s="6" t="n">
+        <v>225652.234993614</v>
+      </c>
       <c r="O395" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31139,14 +31023,10 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q395" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q395" s="4" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
@@ -31212,7 +31092,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N396" s="4" t="n"/>
+      <c r="N396" s="6" t="n">
+        <v>21909.3426680117</v>
+      </c>
       <c r="O396" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31220,14 +31102,10 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q396" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q396" s="4" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
@@ -31293,7 +31171,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N397" s="4" t="n"/>
+      <c r="N397" s="6" t="n">
+        <v>1885.46577647144</v>
+      </c>
       <c r="O397" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31301,14 +31181,10 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q397" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q397" s="4" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
@@ -31374,7 +31250,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N398" s="4" t="n"/>
+      <c r="N398" s="6" t="n">
+        <v>1212.84660038412</v>
+      </c>
       <c r="O398" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31382,14 +31260,10 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q398" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q398" s="4" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
@@ -31455,7 +31329,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N399" s="4" t="n"/>
+      <c r="N399" s="6" t="n">
+        <v>210.806068385812</v>
+      </c>
       <c r="O399" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31463,14 +31339,10 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q399" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q399" s="4" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
@@ -31536,7 +31408,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N400" s="4" t="n"/>
+      <c r="N400" s="6" t="n">
+        <v>367.798078256365</v>
+      </c>
       <c r="O400" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31544,14 +31418,10 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q400" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q400" s="4" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
@@ -31617,7 +31487,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N401" s="4" t="n"/>
+      <c r="N401" s="6" t="n">
+        <v>55.4481074808972</v>
+      </c>
       <c r="O401" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31625,14 +31497,10 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q401" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q401" s="4" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
@@ -31698,7 +31566,9 @@
           <t>Inflación medida por el deflactor del PIB</t>
         </is>
       </c>
-      <c r="N402" s="4" t="n"/>
+      <c r="N402" s="6" t="n">
+        <v>227.093064600296</v>
+      </c>
       <c r="O402" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31706,14 +31576,10 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q402" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q402" s="4" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
@@ -31747,7 +31613,7 @@
         </is>
       </c>
       <c r="G403" s="5" t="n">
-        <v>2026</v>
+        <v>1960</v>
       </c>
       <c r="H403" s="4" t="inlineStr">
         <is>
@@ -31761,25 +31627,27 @@
       </c>
       <c r="J403" s="4" t="inlineStr">
         <is>
-          <t>Deflactor</t>
+          <t>Tipo de cambio</t>
         </is>
       </c>
       <c r="K403" s="4" t="inlineStr">
         <is>
-          <t>deflactor</t>
+          <t>tipo_de_cambio</t>
         </is>
       </c>
       <c r="L403" s="4" t="inlineStr">
         <is>
-          <t>NY.GDP.DEFL.KD.ZG</t>
+          <t>PA.NUS.FCRF</t>
         </is>
       </c>
       <c r="M403" s="4" t="inlineStr">
         <is>
-          <t>Inflación medida por el deflactor del PIB</t>
-        </is>
-      </c>
-      <c r="N403" s="4" t="n"/>
+          <t>Tipo de cambio oficial moneda local por dólar</t>
+        </is>
+      </c>
+      <c r="N403" s="6" t="n">
+        <v>0.00334958333233334</v>
+      </c>
       <c r="O403" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31787,14 +31655,10 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q403" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q403" s="4" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="4" t="inlineStr">
@@ -31828,7 +31692,7 @@
         </is>
       </c>
       <c r="G404" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H404" s="4" t="inlineStr">
         <is>
@@ -31861,7 +31725,7 @@
         </is>
       </c>
       <c r="N404" s="6" t="n">
-        <v>0.00334958333233334</v>
+        <v>0.00334983333233333</v>
       </c>
       <c r="O404" s="4" t="inlineStr">
         <is>
@@ -31870,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31907,7 +31771,7 @@
         </is>
       </c>
       <c r="G405" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H405" s="4" t="inlineStr">
         <is>
@@ -31940,7 +31804,7 @@
         </is>
       </c>
       <c r="N405" s="6" t="n">
-        <v>0.00334983333233333</v>
+        <v>0.00334966666566667</v>
       </c>
       <c r="O405" s="4" t="inlineStr">
         <is>
@@ -31949,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31986,7 +31850,7 @@
         </is>
       </c>
       <c r="G406" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H406" s="4" t="inlineStr">
         <is>
@@ -32019,7 +31883,7 @@
         </is>
       </c>
       <c r="N406" s="6" t="n">
-        <v>0.00334966666566667</v>
+        <v>0.00334966666566666</v>
       </c>
       <c r="O406" s="4" t="inlineStr">
         <is>
@@ -32028,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32065,7 +31929,7 @@
         </is>
       </c>
       <c r="G407" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H407" s="4" t="inlineStr">
         <is>
@@ -32098,7 +31962,7 @@
         </is>
       </c>
       <c r="N407" s="6" t="n">
-        <v>0.00334966666566666</v>
+        <v>0.00435</v>
       </c>
       <c r="O407" s="4" t="inlineStr">
         <is>
@@ -32107,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32144,7 +32008,7 @@
         </is>
       </c>
       <c r="G408" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H408" s="4" t="inlineStr">
         <is>
@@ -32177,7 +32041,7 @@
         </is>
       </c>
       <c r="N408" s="6" t="n">
-        <v>0.00435</v>
+        <v>0.0044</v>
       </c>
       <c r="O408" s="4" t="inlineStr">
         <is>
@@ -32186,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32223,7 +32087,7 @@
         </is>
       </c>
       <c r="G409" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H409" s="4" t="inlineStr">
         <is>
@@ -32265,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32302,7 +32166,7 @@
         </is>
       </c>
       <c r="G410" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H410" s="4" t="inlineStr">
         <is>
@@ -32344,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32381,7 +32245,7 @@
         </is>
       </c>
       <c r="G411" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H411" s="4" t="inlineStr">
         <is>
@@ -32423,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32460,7 +32324,7 @@
         </is>
       </c>
       <c r="G412" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H412" s="4" t="inlineStr">
         <is>
@@ -32502,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32539,7 +32403,7 @@
         </is>
       </c>
       <c r="G413" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H413" s="4" t="inlineStr">
         <is>
@@ -32581,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32618,7 +32482,7 @@
         </is>
       </c>
       <c r="G414" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H414" s="4" t="inlineStr">
         <is>
@@ -32660,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32697,7 +32561,7 @@
         </is>
       </c>
       <c r="G415" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H415" s="4" t="inlineStr">
         <is>
@@ -32730,7 +32594,7 @@
         </is>
       </c>
       <c r="N415" s="6" t="n">
-        <v>0.0044</v>
+        <v>0.0043</v>
       </c>
       <c r="O415" s="4" t="inlineStr">
         <is>
@@ -32739,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32776,7 +32640,7 @@
         </is>
       </c>
       <c r="G416" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H416" s="4" t="inlineStr">
         <is>
@@ -32818,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32855,7 +32719,7 @@
         </is>
       </c>
       <c r="G417" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H417" s="4" t="inlineStr">
         <is>
@@ -32897,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32934,7 +32798,7 @@
         </is>
       </c>
       <c r="G418" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H418" s="4" t="inlineStr">
         <is>
@@ -32976,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33013,7 +32877,7 @@
         </is>
       </c>
       <c r="G419" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H419" s="4" t="inlineStr">
         <is>
@@ -33055,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33092,7 +32956,7 @@
         </is>
       </c>
       <c r="G420" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H420" s="4" t="inlineStr">
         <is>
@@ -33134,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33171,7 +33035,7 @@
         </is>
       </c>
       <c r="G421" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H421" s="4" t="inlineStr">
         <is>
@@ -33213,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33250,7 +33114,7 @@
         </is>
       </c>
       <c r="G422" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H422" s="4" t="inlineStr">
         <is>
@@ -33292,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33329,7 +33193,7 @@
         </is>
       </c>
       <c r="G423" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H423" s="4" t="inlineStr">
         <is>
@@ -33371,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33408,7 +33272,7 @@
         </is>
       </c>
       <c r="G424" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H424" s="4" t="inlineStr">
         <is>
@@ -33450,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33487,7 +33351,7 @@
         </is>
       </c>
       <c r="G425" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H425" s="4" t="inlineStr">
         <is>
@@ -33529,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33566,7 +33430,7 @@
         </is>
       </c>
       <c r="G426" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H426" s="4" t="inlineStr">
         <is>
@@ -33608,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33645,7 +33509,7 @@
         </is>
       </c>
       <c r="G427" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H427" s="4" t="inlineStr">
         <is>
@@ -33678,7 +33542,7 @@
         </is>
       </c>
       <c r="N427" s="6" t="n">
-        <v>0.0043</v>
+        <v>0.00701666666666667</v>
       </c>
       <c r="O427" s="4" t="inlineStr">
         <is>
@@ -33687,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33724,7 +33588,7 @@
         </is>
       </c>
       <c r="G428" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H428" s="4" t="inlineStr">
         <is>
@@ -33757,7 +33621,7 @@
         </is>
       </c>
       <c r="N428" s="6" t="n">
-        <v>0.00701666666666667</v>
+        <v>0.0075</v>
       </c>
       <c r="O428" s="4" t="inlineStr">
         <is>
@@ -33766,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33803,7 +33667,7 @@
         </is>
       </c>
       <c r="G429" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H429" s="4" t="inlineStr">
         <is>
@@ -33836,7 +33700,7 @@
         </is>
       </c>
       <c r="N429" s="6" t="n">
-        <v>0.0075</v>
+        <v>0.00808333333333333</v>
       </c>
       <c r="O429" s="4" t="inlineStr">
         <is>
@@ -33845,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33882,7 +33746,7 @@
         </is>
       </c>
       <c r="G430" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H430" s="4" t="inlineStr">
         <is>
@@ -33915,7 +33779,7 @@
         </is>
       </c>
       <c r="N430" s="6" t="n">
-        <v>0.00808333333333333</v>
+        <v>0.0145</v>
       </c>
       <c r="O430" s="4" t="inlineStr">
         <is>
@@ -33924,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33961,7 +33825,7 @@
         </is>
       </c>
       <c r="G431" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H431" s="4" t="inlineStr">
         <is>
@@ -34003,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34040,7 +33904,7 @@
         </is>
       </c>
       <c r="G432" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H432" s="4" t="inlineStr">
         <is>
@@ -34073,7 +33937,7 @@
         </is>
       </c>
       <c r="N432" s="6" t="n">
-        <v>0.0145</v>
+        <v>0.0346916666666667</v>
       </c>
       <c r="O432" s="4" t="inlineStr">
         <is>
@@ -34082,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34119,7 +33983,7 @@
         </is>
       </c>
       <c r="G433" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H433" s="4" t="inlineStr">
         <is>
@@ -34152,7 +34016,7 @@
         </is>
       </c>
       <c r="N433" s="6" t="n">
-        <v>0.0346916666666667</v>
+        <v>0.0468916666666667</v>
       </c>
       <c r="O433" s="4" t="inlineStr">
         <is>
@@ -34161,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34198,7 +34062,7 @@
         </is>
       </c>
       <c r="G434" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H434" s="4" t="inlineStr">
         <is>
@@ -34231,7 +34095,7 @@
         </is>
       </c>
       <c r="N434" s="6" t="n">
-        <v>0.0468916666666667</v>
+        <v>0.056825</v>
       </c>
       <c r="O434" s="4" t="inlineStr">
         <is>
@@ -34240,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34277,7 +34141,7 @@
         </is>
       </c>
       <c r="G435" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H435" s="4" t="inlineStr">
         <is>
@@ -34310,7 +34174,7 @@
         </is>
       </c>
       <c r="N435" s="6" t="n">
-        <v>0.056825</v>
+        <v>0.0683833333333333</v>
       </c>
       <c r="O435" s="4" t="inlineStr">
         <is>
@@ -34319,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34356,7 +34220,7 @@
         </is>
       </c>
       <c r="G436" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H436" s="4" t="inlineStr">
         <is>
@@ -34389,7 +34253,7 @@
         </is>
       </c>
       <c r="N436" s="6" t="n">
-        <v>0.0683833333333333</v>
+        <v>0.0908416666666667</v>
       </c>
       <c r="O436" s="4" t="inlineStr">
         <is>
@@ -34398,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34435,7 +34299,7 @@
         </is>
       </c>
       <c r="G437" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H437" s="4" t="inlineStr">
         <is>
@@ -34468,7 +34332,7 @@
         </is>
       </c>
       <c r="N437" s="6" t="n">
-        <v>0.0908416666666667</v>
+        <v>0.146858333333333</v>
       </c>
       <c r="O437" s="4" t="inlineStr">
         <is>
@@ -34477,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34514,7 +34378,7 @@
         </is>
       </c>
       <c r="G438" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H438" s="4" t="inlineStr">
         <is>
@@ -34547,7 +34411,7 @@
         </is>
       </c>
       <c r="N438" s="6" t="n">
-        <v>0.146858333333333</v>
+        <v>0.176841666666667</v>
       </c>
       <c r="O438" s="4" t="inlineStr">
         <is>
@@ -34556,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34593,7 +34457,7 @@
         </is>
       </c>
       <c r="G439" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H439" s="4" t="inlineStr">
         <is>
@@ -34626,7 +34490,7 @@
         </is>
       </c>
       <c r="N439" s="6" t="n">
-        <v>0.176841666666667</v>
+        <v>0.41735</v>
       </c>
       <c r="O439" s="4" t="inlineStr">
         <is>
@@ -34635,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34672,7 +34536,7 @@
         </is>
       </c>
       <c r="G440" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H440" s="4" t="inlineStr">
         <is>
@@ -34705,7 +34569,7 @@
         </is>
       </c>
       <c r="N440" s="6" t="n">
-        <v>0.41735</v>
+        <v>0.488633333333333</v>
       </c>
       <c r="O440" s="4" t="inlineStr">
         <is>
@@ -34714,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34751,7 +34615,7 @@
         </is>
       </c>
       <c r="G441" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H441" s="4" t="inlineStr">
         <is>
@@ -34784,7 +34648,7 @@
         </is>
       </c>
       <c r="N441" s="6" t="n">
-        <v>0.488633333333333</v>
+        <v>0.547566666666667</v>
       </c>
       <c r="O441" s="4" t="inlineStr">
         <is>
@@ -34793,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34830,7 +34694,7 @@
         </is>
       </c>
       <c r="G442" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H442" s="4" t="inlineStr">
         <is>
@@ -34863,7 +34727,7 @@
         </is>
       </c>
       <c r="N442" s="6" t="n">
-        <v>0.547566666666667</v>
+        <v>0.605725</v>
       </c>
       <c r="O442" s="4" t="inlineStr">
         <is>
@@ -34872,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34909,7 +34773,7 @@
         </is>
       </c>
       <c r="G443" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H443" s="4" t="inlineStr">
         <is>
@@ -34942,7 +34806,7 @@
         </is>
       </c>
       <c r="N443" s="6" t="n">
-        <v>0.605725</v>
+        <v>0.6799666666666671</v>
       </c>
       <c r="O443" s="4" t="inlineStr">
         <is>
@@ -34951,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34988,7 +34852,7 @@
         </is>
       </c>
       <c r="G444" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H444" s="4" t="inlineStr">
         <is>
@@ -35021,7 +34885,7 @@
         </is>
       </c>
       <c r="N444" s="6" t="n">
-        <v>0.6799666666666671</v>
+        <v>0.723658333333334</v>
       </c>
       <c r="O444" s="4" t="inlineStr">
         <is>
@@ -35030,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35067,7 +34931,7 @@
         </is>
       </c>
       <c r="G445" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H445" s="4" t="inlineStr">
         <is>
@@ -35100,7 +34964,7 @@
         </is>
       </c>
       <c r="N445" s="6" t="n">
-        <v>0.723658333333334</v>
+        <v>1.16095</v>
       </c>
       <c r="O445" s="4" t="inlineStr">
         <is>
@@ -35109,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35146,7 +35010,7 @@
         </is>
       </c>
       <c r="G446" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H446" s="4" t="inlineStr">
         <is>
@@ -35179,7 +35043,7 @@
         </is>
       </c>
       <c r="N446" s="6" t="n">
-        <v>1.16095</v>
+        <v>1.60695833333333</v>
       </c>
       <c r="O446" s="4" t="inlineStr">
         <is>
@@ -35188,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35225,7 +35089,7 @@
         </is>
       </c>
       <c r="G447" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H447" s="4" t="inlineStr">
         <is>
@@ -35258,7 +35122,7 @@
         </is>
       </c>
       <c r="N447" s="6" t="n">
-        <v>1.60695833333333</v>
+        <v>1.89133333333333</v>
       </c>
       <c r="O447" s="4" t="inlineStr">
         <is>
@@ -35267,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35304,7 +35168,7 @@
         </is>
       </c>
       <c r="G448" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H448" s="4" t="inlineStr">
         <is>
@@ -35337,7 +35201,7 @@
         </is>
       </c>
       <c r="N448" s="6" t="n">
-        <v>1.89133333333333</v>
+        <v>2.08975</v>
       </c>
       <c r="O448" s="4" t="inlineStr">
         <is>
@@ -35346,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35383,7 +35247,7 @@
         </is>
       </c>
       <c r="G449" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H449" s="4" t="inlineStr">
         <is>
@@ -35416,7 +35280,7 @@
         </is>
       </c>
       <c r="N449" s="6" t="n">
-        <v>2.08975</v>
+        <v>2.147</v>
       </c>
       <c r="O449" s="4" t="inlineStr">
         <is>
@@ -35425,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35462,7 +35326,7 @@
         </is>
       </c>
       <c r="G450" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H450" s="4" t="inlineStr">
         <is>
@@ -35504,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35541,7 +35405,7 @@
         </is>
       </c>
       <c r="G451" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H451" s="4" t="inlineStr">
         <is>
@@ -35583,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35620,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H452" s="4" t="inlineStr">
         <is>
@@ -35662,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35699,7 +35563,7 @@
         </is>
       </c>
       <c r="G453" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H453" s="4" t="inlineStr">
         <is>
@@ -35732,7 +35596,7 @@
         </is>
       </c>
       <c r="N453" s="6" t="n">
-        <v>2.147</v>
+        <v>2.58206031746032</v>
       </c>
       <c r="O453" s="4" t="inlineStr">
         <is>
@@ -35741,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35778,7 +35642,7 @@
         </is>
       </c>
       <c r="G454" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H454" s="4" t="inlineStr">
         <is>
@@ -35811,7 +35675,7 @@
         </is>
       </c>
       <c r="N454" s="6" t="n">
-        <v>2.58206031746032</v>
+        <v>4.2893</v>
       </c>
       <c r="O454" s="4" t="inlineStr">
         <is>
@@ -35820,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35857,7 +35721,7 @@
         </is>
       </c>
       <c r="G455" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H455" s="4" t="inlineStr">
         <is>
@@ -35899,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35936,7 +35800,7 @@
         </is>
       </c>
       <c r="G456" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H456" s="4" t="inlineStr">
         <is>
@@ -35969,7 +35833,7 @@
         </is>
       </c>
       <c r="N456" s="6" t="n">
-        <v>4.2893</v>
+        <v>6.04796184166667</v>
       </c>
       <c r="O456" s="4" t="inlineStr">
         <is>
@@ -35978,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36015,7 +35879,7 @@
         </is>
       </c>
       <c r="G457" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H457" s="4" t="inlineStr">
         <is>
@@ -36048,7 +35912,7 @@
         </is>
       </c>
       <c r="N457" s="6" t="n">
-        <v>6.04796184166667</v>
+        <v>6.2842</v>
       </c>
       <c r="O457" s="4" t="inlineStr">
         <is>
@@ -36057,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36094,7 +35958,7 @@
         </is>
       </c>
       <c r="G458" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H458" s="4" t="inlineStr">
         <is>
@@ -36136,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36173,7 +36037,7 @@
         </is>
       </c>
       <c r="G459" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H459" s="4" t="inlineStr">
         <is>
@@ -36206,7 +36070,7 @@
         </is>
       </c>
       <c r="N459" s="6" t="n">
-        <v>6.2842</v>
+        <v>9.257344444441671</v>
       </c>
       <c r="O459" s="4" t="inlineStr">
         <is>
@@ -36215,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36252,7 +36116,7 @@
         </is>
       </c>
       <c r="G460" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H460" s="4" t="inlineStr">
         <is>
@@ -36285,7 +36149,7 @@
         </is>
       </c>
       <c r="N460" s="6" t="n">
-        <v>9.257344444441671</v>
+        <v>9.975</v>
       </c>
       <c r="O460" s="4" t="inlineStr">
         <is>
@@ -36294,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36331,7 +36195,7 @@
         </is>
       </c>
       <c r="G461" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H461" s="4" t="inlineStr">
         <is>
@@ -36363,9 +36227,7 @@
           <t>Tipo de cambio oficial moneda local por dólar</t>
         </is>
       </c>
-      <c r="N461" s="6" t="n">
-        <v>9.975</v>
-      </c>
+      <c r="N461" s="4" t="n"/>
       <c r="O461" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36373,7 +36235,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36410,7 +36272,7 @@
         </is>
       </c>
       <c r="G462" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H462" s="4" t="inlineStr">
         <is>
@@ -36450,7 +36312,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36487,7 +36349,7 @@
         </is>
       </c>
       <c r="G463" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H463" s="4" t="inlineStr">
         <is>
@@ -36527,7 +36389,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36564,7 +36426,7 @@
         </is>
       </c>
       <c r="G464" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H464" s="4" t="inlineStr">
         <is>
@@ -36604,7 +36466,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36641,7 +36503,7 @@
         </is>
       </c>
       <c r="G465" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H465" s="4" t="inlineStr">
         <is>
@@ -36681,7 +36543,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36718,7 +36580,7 @@
         </is>
       </c>
       <c r="G466" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H466" s="4" t="inlineStr">
         <is>
@@ -36758,7 +36620,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36795,7 +36657,7 @@
         </is>
       </c>
       <c r="G467" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H467" s="4" t="inlineStr">
         <is>
@@ -36835,7 +36697,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36872,7 +36734,7 @@
         </is>
       </c>
       <c r="G468" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H468" s="4" t="inlineStr">
         <is>
@@ -36912,87 +36774,10 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
-    </row>
-    <row r="469">
-      <c r="A469" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B469" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C469" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D469" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E469" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F469" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G469" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H469" s="4" t="inlineStr">
-        <is>
-          <t>Precios e inflación</t>
-        </is>
-      </c>
-      <c r="I469" s="4" t="inlineStr">
-        <is>
-          <t>precios_e_inflacion</t>
-        </is>
-      </c>
-      <c r="J469" s="4" t="inlineStr">
-        <is>
-          <t>Tipo de cambio</t>
-        </is>
-      </c>
-      <c r="K469" s="4" t="inlineStr">
-        <is>
-          <t>tipo_de_cambio</t>
-        </is>
-      </c>
-      <c r="L469" s="4" t="inlineStr">
-        <is>
-          <t>PA.NUS.FCRF</t>
-        </is>
-      </c>
-      <c r="M469" s="4" t="inlineStr">
-        <is>
-          <t>Tipo de cambio oficial moneda local por dólar</t>
-        </is>
-      </c>
-      <c r="N469" s="4" t="n"/>
-      <c r="O469" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P469" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q469" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -37074,7 +36859,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -37095,7 +36880,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18118,7 +18118,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18272,7 +18272,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18580,7 +18580,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19042,7 +19042,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20047,7 +20047,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20598,7 +20598,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20983,7 +20983,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21214,7 +21214,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21291,7 +21291,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21445,7 +21445,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22523,7 +22523,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22600,7 +22600,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22677,7 +22677,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22754,7 +22754,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23141,7 +23141,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23220,7 +23220,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23378,7 +23378,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23615,7 +23615,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24010,7 +24010,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24089,7 +24089,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24168,7 +24168,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24405,7 +24405,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24484,7 +24484,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24721,7 +24721,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24958,7 +24958,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25037,7 +25037,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25432,7 +25432,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25511,7 +25511,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25748,7 +25748,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25902,7 +25902,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26056,7 +26056,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26210,7 +26210,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26287,7 +26287,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36235,7 +36235,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36466,7 +36466,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36620,7 +36620,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36697,7 +36697,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36774,7 +36774,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36859,7 +36859,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18118,7 +18118,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18272,7 +18272,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18580,7 +18580,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19042,7 +19042,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20047,7 +20047,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20598,7 +20598,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20983,7 +20983,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21214,7 +21214,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21291,7 +21291,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21445,7 +21445,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22523,7 +22523,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22600,7 +22600,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22677,7 +22677,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22754,7 +22754,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23141,7 +23141,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23220,7 +23220,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23378,7 +23378,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23615,7 +23615,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24010,7 +24010,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24089,7 +24089,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24168,7 +24168,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24405,7 +24405,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24484,7 +24484,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24721,7 +24721,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24958,7 +24958,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25037,7 +25037,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25432,7 +25432,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25511,7 +25511,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25748,7 +25748,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25902,7 +25902,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26056,7 +26056,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26210,7 +26210,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26287,7 +26287,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36235,7 +36235,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36466,7 +36466,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36620,7 +36620,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36697,7 +36697,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36774,7 +36774,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36859,7 +36859,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18118,7 +18118,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18272,7 +18272,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18580,7 +18580,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19042,7 +19042,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20047,7 +20047,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20598,7 +20598,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20983,7 +20983,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21214,7 +21214,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21291,7 +21291,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21445,7 +21445,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22523,7 +22523,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22600,7 +22600,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22677,7 +22677,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22754,7 +22754,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23141,7 +23141,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23220,7 +23220,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23378,7 +23378,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23615,7 +23615,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24010,7 +24010,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24089,7 +24089,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24168,7 +24168,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24405,7 +24405,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24484,7 +24484,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24721,7 +24721,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24958,7 +24958,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25037,7 +25037,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25432,7 +25432,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25511,7 +25511,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25748,7 +25748,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25902,7 +25902,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26056,7 +26056,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26210,7 +26210,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26287,7 +26287,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36235,7 +36235,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36466,7 +36466,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36620,7 +36620,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36697,7 +36697,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36774,7 +36774,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36859,7 +36859,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
